--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -549,6 +549,36 @@
           <t>Statut</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Horaires</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Téléphone</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Site web</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Nb avis</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -561,7 +591,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Basilique Sainte Rita</t>
+          <t>Église Sainte Rita</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -639,6 +669,27 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Musée principal (Zongo/Haie Vive) : lun 14h-19h, mar-sam 10h-19h, fermé dim. LAB (Fidjrossè) : lun-ven ~9h-18h, fermé dim.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>+229 91 20 70 19</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.fondation-zinsou.org</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -684,6 +735,12 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="M4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -729,6 +786,12 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="M5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -774,6 +837,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>+229 21 38 17 84</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -819,6 +893,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9h-18h tous les jours</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -864,6 +949,22 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Tous les jours, environ 8h-19h</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>+229 41 44 87 06</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -909,6 +1010,12 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="M9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -954,6 +1061,22 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+229 21 34 10 21</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>79</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Possiblement fermé pour rénovation depuis 2026 — vérifier avant de s'y rendre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -999,6 +1122,12 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="M11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1044,6 +1173,12 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1089,6 +1224,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>+229 96 53 60 42</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1134,6 +1280,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>+229 20 21 25 54</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1179,6 +1336,21 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Visites guidées lun-ven 8h30/10h30/15h30/17h, sam 8h30/10h30/16h</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>+229 01 60 93 33 34</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://songhai.org</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1224,6 +1396,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Messes semaine 6h, 12h45, 18h ; dimanche 7h, 9h, 10h30, 19h</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1314,6 +1491,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1359,6 +1541,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Patrimoine culturel immatériel (UNESCO) ; le berceau historique documenté est plutôt Kétou/Savè.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1449,6 +1636,22 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Tous les jours, 9h-18h</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>+229 22 50 03 14</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1457,21 +1660,21 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Musée historique d'Abomey</t>
+          <t>Place Béhanzin (Place Goho)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Musée dans l'ancien palais royal, artefacts et trônes royaux.</t>
+          <t>Place centrale avec statue du roi Béhanzin, symbole de résistance.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1481,32 +1684,43 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7.1863091, 1.9943789</t>
+          <t>7.1842529, 2.0078158</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1863091,1.9943789</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1842529,2.0078158</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Un état d'entretien dégradé a été signalé par la presse locale.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Atlantique/Zou</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Place Béhanzin (Place Goho)</t>
+          <t>Forêt classée de la Lama</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1516,22 +1730,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Place centrale avec statue du roi Béhanzin, symbole de résistance.</t>
+          <t>Grande forêt naturelle, observation d'animaux et de flore variée.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Abomey, Zou</t>
+          <t>Toffo, Atlantique / Zogbodomey, Zou</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7.1842529, 2.0078158</t>
+          <t>6.9179281, 2.1662158</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1842529,2.0078158</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9179281,2.1662158</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1543,45 +1757,50 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Collines</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Forêt classée de la Lama</t>
+          <t>Grotte mariale de Dassa-Zoumé</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Grande forêt naturelle, observation d'animaux et de flore variée.</t>
+          <t>Lieu de pèlerinage catholique niché dans les collines.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Zou/Ouémé (zone Lama)</t>
+          <t>Dassa-Zoumé, Collines</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6.9179281, 2.1662158</t>
+          <t>7.7752876, 2.1865136</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9179281,2.1662158</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7752876,2.1865136</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ouvert toute l'année ; grand pèlerinage fin août</t>
         </is>
       </c>
     </row>
@@ -1592,11 +1811,11 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Grotte mariale de Dassa-Zoumé</t>
+          <t>Savalou (ville historique, culte vaudou)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1606,22 +1825,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Lieu de pèlerinage catholique niché dans les collines.</t>
+          <t>Ville traditionnelle marquée par la royauté locale et le culte vaudou.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Dassa-Zoumé, Collines</t>
+          <t>Savalou, Collines</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7.7752876, 2.1865136</t>
+          <t>7.9301365, 1.9710284</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7752876,2.1865136</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9301365,1.9710284</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1633,40 +1852,40 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Collines</t>
+          <t>Mono</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Savalou (ville historique, culte vaudou)</t>
+          <t>Plage de Grand-Popo</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ville traditionnelle marquée par la royauté locale et le culte vaudou.</t>
+          <t>Plage réputée du littoral béninois, tourisme balnéaire.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Savalou, Collines</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>7.9301365, 1.9710284</t>
+          <t>6.2639324, 1.7417143</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9301365,1.9710284</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2639324,1.7417143</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1682,41 +1901,51 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Plage de Grand-Popo</t>
+          <t>Village de Possotomè</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Plage réputée du littoral béninois, tourisme balnéaire.</t>
+          <t>Village au bord du lac Ahémé, source d'eau thermale.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Possotomè, Bopa, Mono</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6.2639324, 1.7417143</t>
+          <t>6.520838, 1.9625132</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2639324,1.7417143</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.520838,1.9625132</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>+229 95 28 52 20</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://www.ecobenin.org/possotome</t>
         </is>
       </c>
     </row>
@@ -1727,11 +1956,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Village de Possotomè</t>
+          <t>Bouche du Roy</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1741,28 +1970,44 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Village au bord du lac Ahémé, source d'eau thermale.</t>
+          <t>Embouchure spectaculaire entre océan, lagune et mangrove.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Possotomè, Bopa, Mono</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6.520838, 1.9625132</t>
+          <t>6.2922216, 1.917286</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.520838,1.9625132</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>+229 60 63 08 18</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://www.boucheduroy.bj</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1772,11 +2017,11 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Bouche du Roy</t>
+          <t>Ville de Lokossa</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1786,42 +2031,47 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Embouchure spectaculaire entre océan, lagune et mangrove.</t>
+          <t>Chef-lieu du département du Mono.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Lokossa, Mono</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6.2922216, 1.917286</t>
+          <t>6.6448093, 1.7198215</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.6448093,1.7198215</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://lokossa.mairie.bj/fr/decouverte</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Mono</t>
+          <t>Atacora</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ville de Lokossa</t>
+          <t>Parc national de la Pendjari</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1831,27 +2081,37 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Chef-lieu du département du Mono.</t>
+          <t>Réserve faunique majeure, safaris et observation de la faune africaine.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Lokossa, Mono</t>
+          <t>Atacora</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6.6448093, 1.7198215</t>
+          <t>11.2481125, 1.5983959</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.6448093,1.7198215</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ouvert toute l'année ; safaris recommandés 6h-11h et 16h-tombée de la nuit</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
     </row>
@@ -1862,11 +2122,11 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Parc national de la Pendjari</t>
+          <t>Villages Tata Somba</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1876,22 +2136,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Réserve faunique majeure, safaris et observation de la faune africaine.</t>
+          <t>Habitats traditionnels fortifiés des Batammariba.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
+          <t>Natitingou/Boukoumbé, Atacora</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11.2481125, 1.5983959</t>
+          <t>10.3091173, 1.3735244</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1907,36 +2167,36 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Villages Tata Somba</t>
+          <t>Cascades de Tanougou</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Habitats traditionnels fortifiés des Batammariba.</t>
+          <t>Chutes d'eau et bassins naturels dans les montagnes de l'Atacora.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Natitingou/Boukoumbé, Atacora</t>
+          <t>Tanongou, Atacora</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10.3091173, 1.3735244</t>
+          <t>10.8121477, 1.4363443</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1952,41 +2212,51 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Cascades de Tanougou</t>
+          <t>Musée régional de Natitingou</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Chutes d'eau et bassins naturels dans les montagnes de l'Atacora.</t>
+          <t>Musée sur les traditions socioculturelles de la région.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tanongou, Atacora</t>
+          <t>Natitingou, Atacora</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10.8121477, 1.4363443</t>
+          <t>10.3106873, 1.3802711</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3106873,1.3802711</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Lun-Ven 8h30-18h30, Sam-Dim 9h-18h30</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>+229 97 88 10 80</t>
         </is>
       </c>
     </row>
@@ -1997,36 +2267,36 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Musée régional de Natitingou</t>
+          <t>Chaîne de l'Atacora</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Musée sur les traditions socioculturelles de la région.</t>
+          <t>Massif montagneux, randonnée et paysages du nord-ouest du Bénin.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Natitingou, Atacora</t>
+          <t>Atacora (zone)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10.3106873, 1.3802711</t>
+          <t>10.75, 1.5</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3106873,1.3802711</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.75,1.5</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2038,15 +2308,15 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
+          <t>Borgou/Donga</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Chaîne de l'Atacora</t>
+          <t>Forêt classée de Wari-Maro</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2056,27 +2326,32 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Massif montagneux, randonnée et paysages du nord-ouest du Bénin.</t>
+          <t>Réserve forestière et faunique de la région.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Atacora (zone)</t>
+          <t>Tchaourou, Borgou / Bassila, Donga</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10.75, 1.5</t>
+          <t>8.9622901, 2.1843285</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.75,1.5</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Statut en évolution : fusion annoncée avec la forêt des Monts Kouffé en un nouveau parc national (déc. gouvernementale nov. 2025).</t>
         </is>
       </c>
     </row>
@@ -2087,56 +2362,61 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Forêt classée de Wari-Maro</t>
+          <t>Village de Bassila</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Réserve forestière et faunique de la région.</t>
+          <t>Commune forestière du sud de la Donga.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Donga/Collines (zone Wari-Maro)</t>
+          <t>Bassila, Donga</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8.9622901, 2.1843285</t>
+          <t>9.006393, 1.6639235</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.006393,1.6639235</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>+229 23 30 11 76</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Donga</t>
+          <t>Borgou</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Village de Bassila</t>
+          <t>Musée de plein air de Parakou</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2146,27 +2426,42 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Commune forestière du sud de la Donga.</t>
+          <t>Musée d'art et traditions populaires du nord du Bénin.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Bassila, Donga</t>
+          <t>Parakou, Borgou</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9.006393, 1.6639235</t>
+          <t>9.3279386, 2.6174022</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.006393,1.6639235</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Tous les jours 9h-12h et 15h-18h30, sauf jours fériés</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>+229 23 61 05 78</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
         </is>
       </c>
     </row>
@@ -2177,41 +2472,56 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Musée de plein air de Parakou</t>
+          <t>Fête de la Gaani</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Événement</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Musée d'art et traditions populaires du nord du Bénin.</t>
+          <t>Grande manifestation culturelle annuelle des Batombu.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Parakou, Borgou</t>
+          <t>Nikki, Borgou</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>9.3279386, 2.6174022</t>
+          <t>9.9276076, 3.2167913</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9276076,3.2167913</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3 jours fin août (ex. 25-27 août 2026)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://gaani.bj</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Anciennement orthographié « Gani » ; deux fiches en doublon fusionnées.</t>
         </is>
       </c>
     </row>
@@ -2222,21 +2532,21 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fête de la Gani (Nikki)</t>
+          <t>Palais royal de Nikki</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Événement</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Grande manifestation culturelle annuelle des Batombu.</t>
+          <t>Capitale historique des Batombu, siège royal.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2246,12 +2556,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9.9276076, 3.2167913</t>
+          <t>9.9363278, 3.2105884</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9276076,3.2167913</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9363278,3.2105884</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2263,15 +2573,15 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Palais royal de Nikki</t>
+          <t>Parc national du W</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2281,27 +2591,32 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Capitale historique des Batombu, siège royal.</t>
+          <t>Parc transfrontalier Bénin-Niger-Burkina Faso, UNESCO.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Nikki, Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>9.9363278, 3.2105884</t>
+          <t>12.0408333, 3.0341667</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9363278,3.2105884</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Ouvert toute l'année</t>
         </is>
       </c>
     </row>
@@ -2312,36 +2627,36 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Parc national du W</t>
+          <t>Fleuve Niger (rives)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Parc transfrontalier Bénin-Niger-Burkina Faso, UNESCO.</t>
+          <t>Rives du fleuve Niger, paysages et activités fluviales.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Alibori</t>
+          <t>Malanville, Alibori</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>12.0408333, 3.0341667</t>
+          <t>11.8633332, 3.3842473</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8633332,3.3842473</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2357,36 +2672,36 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fleuve Niger (rives)</t>
+          <t>Ville de Kandi</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Rives du fleuve Niger, paysages et activités fluviales.</t>
+          <t>Chef-lieu du département de l'Alibori.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Malanville, Alibori</t>
+          <t>Kandi, Alibori</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>11.8633332, 3.3842473</t>
+          <t>11.1305191, 2.9325785</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8633332,3.3842473</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2396,47 +2711,9 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Ville de Kandi</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Site touristique</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Chef-lieu du département de l'Alibori.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Kandi, Alibori</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>11.1305191, 2.9325785</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
         </is>
       </c>
     </row>
@@ -2463,28 +2740,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2496,7 +2772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2550,6 +2826,36 @@
           <t>Statut</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Horaires</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Téléphone</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Site web</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Nb avis</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Remarque</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2592,6 +2898,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>+229 53 64 91 65</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.beachsandhotel.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2634,6 +2950,12 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2676,6 +2998,27 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>+229 95 21 40 40</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://easyhotelsbenin.com</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Notes très divergentes selon la plateforme (2/5 TripAdvisor vs retours positifs ailleurs).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2718,6 +3061,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>+229 01 54 28 44 44</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/aquamazone229/accueil</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2844,6 +3197,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>+229 01 45 46 42 88</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://nativehotels.net</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2886,6 +3249,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>+229 96 18 21 94</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Localisation précise : Kpomassè, lac Ahémé (à ~20 min de Ouidah)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2928,6 +3301,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Tous les jours 9h-22h</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2970,6 +3348,21 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24h/24, 7j/7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>+229 01 66 04 40 12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://nadalevasiontours.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3012,6 +3405,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>+229 96 74 06 13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.visit-ganvie-tourism.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3054,6 +3457,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Format étendu « Vodun Days » sur 2-3 jours (ex. 8-10 janvier 2026)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://vodundays.bj</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3096,6 +3509,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://artresidence.bj</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3138,6 +3562,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>+229 65 00 38 65</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3264,6 +3699,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Marché quotidien, plus animé mercredi et samedi matin</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3348,6 +3788,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3516,6 +3961,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>+229 01 55 40 98 78</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3558,6 +4014,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>+229 63 13 64 64</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3600,11 +4067,22 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9h-18h (une source indique 8h-17h)</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M26" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Atlantique/Zou</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -3624,7 +4102,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Zou/Ouémé (zone Lama)</t>
+          <t>Toffo, Atlantique / Zogbodomey, Zou</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3684,6 +4162,22 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>+229 22 53 08 89</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://jecohotels.com</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3726,6 +4220,17 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>+229 94 47 21 35</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3768,6 +4273,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://loubna-hotel.com</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Référencé en ligne sous le nom « Hôtel Loubna Évolution ».</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3810,6 +4325,11 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Site ouvert toute l'année ; pèlerinage vers le 15 août</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3898,7 +4418,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Couffo</t>
+          <t>Mono</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3908,33 +4428,49 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Arnogos</t>
+          <t>Awale Plage</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Hôtel accessible sur la RN2 à Azové.</t>
+          <t>Hôtel-restaurant en bord de plage à Grand-Popo.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Azové, Couffo</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6.9326883, 1.7079479</t>
+          <t>6.270213, 1.786942</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9326883,1.7079479</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.270213,1.786942</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>+229 58 01 01 12</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://www.hotel-benin-awaleplage.com</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M34" t="n">
+        <v>137</v>
       </c>
     </row>
     <row r="35">
@@ -3950,12 +4486,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Awale Plage</t>
+          <t>ASVA Beach Resort</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Hôtel-restaurant en bord de plage à Grand-Popo.</t>
+          <t>Hôtel proche de la plage, ambiance festive.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3965,12 +4501,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6.270213, 1.786942</t>
+          <t>6.2757733, 1.8104271</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.270213,1.786942</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2757733,1.8104271</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3992,12 +4528,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ASVA Beach Resort</t>
+          <t>Millenium Popo Beach Hôtel</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Hôtel proche de la plage, ambiance festive.</t>
+          <t>Grand complexe hôtelier en bord de mer.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4007,18 +4543,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6.2757733, 1.8104271</t>
+          <t>6.2518431, 1.6979677</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2757733,1.8104271</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2518431,1.6979677</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>+229 6860 1111</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="37">
@@ -4027,19 +4574,19 @@
           <t>Mono</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Millenium Popo Beach Hôtel</t>
+          <t>Excursions avec BAKOLO Tours</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Grand complexe hôtelier en bord de mer.</t>
+          <t>Agence locale pour circuits sur mesure dans la région.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4049,17 +4596,27 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6.2518431, 1.6979677</t>
+          <t>6.2772786, 1.8037903</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2518431,1.6979677</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2772786,1.8037903</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>+229 94 69 96 89</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.bakolotours.com</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4633,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Excursions avec BAKOLO Tours</t>
+          <t>Sortie bateau vers la Bouche du Roy</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Agence locale pour circuits sur mesure dans la région.</t>
+          <t>Excursion vers l'embouchure entre océan et lagune.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4091,12 +4648,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6.2772786, 1.8037903</t>
+          <t>6.2922216, 1.917286</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2772786,1.8037903</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4108,43 +4665,54 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Mono</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Atacora</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sortie bateau vers la Bouche du Roy</t>
+          <t>Hôtel Bellevue</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Excursion vers l'embouchure entre océan et lagune.</t>
+          <t>Hôtel historique et chaleureux à Natitingou.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Natitingou, Atacora</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6.2922216, 1.917286</t>
+          <t>10.3059893, 1.3856433</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3059893,1.3856433</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>+229 23 82 13 36</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -4160,12 +4728,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Bellevue</t>
+          <t>Hôtel Tata Somba</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Hôtel historique et chaleureux à Natitingou.</t>
+          <t>Hôtel au pied des collines, proche des villages Tata Somba.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4175,18 +4743,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10.3059893, 1.3856433</t>
+          <t>10.3091173, 1.3735244</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3059893,1.3856433</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="L40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M40" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="41">
@@ -4202,12 +4776,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Tata Somba</t>
+          <t>Hôtel Totora</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Hôtel au pied des collines, proche des villages Tata Somba.</t>
+          <t>Hôtel avec piscine et vue sur les montagnes.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4217,18 +4791,34 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10.3091173, 1.3735244</t>
+          <t>10.3181651, 1.3738271</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3181651,1.3738271</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>+229 62 23 62 52</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.hoteltotora.com</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>375</v>
       </c>
     </row>
     <row r="42">
@@ -4237,39 +4827,49 @@
           <t>Atacora</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Totora</t>
+          <t>Safari au Parc national de la Pendjari</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Hôtel avec piscine et vue sur les montagnes.</t>
+          <t>Safari guidé pour observer lions, éléphants, hippopotames.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Natitingou, Atacora</t>
+          <t>Atacora</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10.3181651, 1.3738271</t>
+          <t>11.2481125, 1.5983959</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3181651,1.3738271</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
     </row>
@@ -4286,27 +4886,27 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Safari au Parc national de la Pendjari</t>
+          <t>Visite des villages Tata Somba</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Safari guidé pour observer lions, éléphants, hippopotames.</t>
+          <t>Découverte des habitats fortifiés traditionnels.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
+          <t>Natitingou/Boukoumbé, Atacora</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11.2481125, 1.5983959</t>
+          <t>10.3091173, 1.3735244</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -4328,27 +4928,27 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Visite des villages Tata Somba</t>
+          <t>Randonnée aux cascades de Tanougou</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Découverte des habitats fortifiés traditionnels.</t>
+          <t>Baignade et randonnée dans un cadre naturel.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Natitingou/Boukoumbé, Atacora</t>
+          <t>Tanongou, Atacora</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10.3091173, 1.3735244</t>
+          <t>10.8121477, 1.4363443</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4360,42 +4960,47 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Donga</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Randonnée aux cascades de Tanougou</t>
+          <t>Motel Du Lac</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Baignade et randonnée dans un cadre naturel.</t>
+          <t>Hôtel familial réputé pour sa cuisine, à Djougou.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tanongou, Atacora</t>
+          <t>Djougou, Donga</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>10.8121477, 1.4363443</t>
+          <t>9.6802129, 1.6527047</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6802129,1.6527047</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>+229 97 54 06 56</t>
         </is>
       </c>
     </row>
@@ -4412,12 +5017,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Motel Du Lac</t>
+          <t>Hôtel de la Donga</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Hôtel familial réputé pour sa cuisine, à Djougou.</t>
+          <t>Hôtel simple et pratique à Djougou.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4427,18 +5032,29 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9.6802129, 1.6527047</t>
+          <t>9.6997379, 1.6732916</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6802129,1.6527047</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6997379,1.6732916</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>+229 23 80 15 72</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -4454,12 +5070,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Hôtel de la Donga</t>
+          <t>Hôtel Cathas</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Hôtel simple et pratique à Djougou.</t>
+          <t>Hôtel accessible au centre de Djougou.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4469,54 +5085,59 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9.6997379, 1.6732916</t>
+          <t>9.6989611, 1.6729295</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6997379,1.6732916</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6989611,1.6729295</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>+229 66 03 37 51</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Donga</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+          <t>Borgou/Donga</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Cathas</t>
+          <t>Découverte de la Forêt classée de Wari-Maro</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Hôtel accessible au centre de Djougou.</t>
+          <t>Randonnée nature et observation de la faune.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Djougou, Donga</t>
+          <t>Tchaourou, Borgou / Bassila, Donga</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9.6989611, 1.6729295</t>
+          <t>8.9622901, 2.1843285</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6989611,1.6729295</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4528,37 +5149,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Donga</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Borgou</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Découverte de la Forêt classée de Wari-Maro</t>
+          <t>Ola Luxury Hôtel</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Randonnée nature et observation de la faune.</t>
+          <t>Hôtel confortable et bien noté à Parakou.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Zone Wari-Maro, Donga</t>
+          <t>Parakou, Borgou</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8.9622901, 2.1843285</t>
+          <t>9.3553016, 2.6330228</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3553016,2.6330228</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4580,12 +5201,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Ola Luxury Hôtel</t>
+          <t>Kobourou City Hôtel</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable et bien noté à Parakou.</t>
+          <t>Grand hôtel avec piscine à Parakou.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4595,18 +5216,24 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9.3553016, 2.6330228</t>
+          <t>9.3664096, 2.6247833</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3553016,2.6330228</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3664096,2.6247833</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -4622,12 +5249,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Kobourou City Hôtel</t>
+          <t>Hôtel Iya-Oasis</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Grand hôtel avec piscine à Parakou.</t>
+          <t>Hôtel au décor traditionnel, très bien noté à Parakou.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4637,18 +5264,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>9.3664096, 2.6247833</t>
+          <t>9.3457835, 2.6373219</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3664096,2.6247833</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3457835,2.6373219</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="L51" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -4657,19 +5290,19 @@
           <t>Borgou</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Iya-Oasis</t>
+          <t>Visite du musée de plein air de Parakou</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Hôtel au décor traditionnel, très bien noté à Parakou.</t>
+          <t>Découverte de l'art et des traditions du nord du Bénin.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4679,54 +5312,69 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9.3457835, 2.6373219</t>
+          <t>9.3279386, 2.6174022</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3457835,2.6373219</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Tous les jours 9h-12h et 15h-18h30, sauf jours fériés</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>+229 23 61 05 78</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Alibori</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Visite du musée de plein air de Parakou</t>
+          <t>Hôtel Séjour du Sahel</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Découverte de l'art et des traditions du nord du Bénin.</t>
+          <t>Hôtel propre et sécurisé à Malanville.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Parakou, Borgou</t>
+          <t>Malanville, Alibori</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>9.3279386, 2.6174022</t>
+          <t>11.8523034, 3.389122</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8523034,3.389122</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4738,37 +5386,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Événement</t>
+          <t>Alibori</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Fête de la Gani</t>
+          <t>Safari au Parc national du W</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Grande manifestation culturelle annuelle des Batombu à Nikki.</t>
+          <t>Observation de la faune dans le parc transfrontalier UNESCO.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nikki, Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9.9276076, 3.2167913</t>
+          <t>12.0408333, 3.0341667</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9276076,3.2167913</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4776,88 +5424,23 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Hôtel Séjour du Sahel</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Hôtel propre et sécurisé à Malanville.</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Malanville, Alibori</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>11.8523034, 3.389122</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=11.8523034,3.389122</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Safari au Parc national du W</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Observation de la faune dans le parc transfrontalier UNESCO.</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>12.0408333, 3.0341667</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
         </is>
       </c>
     </row>
@@ -4896,29 +5479,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1504,61 +1504,56 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sociétés de masques Guèlèdè, Sakété</t>
+          <t>Ville de Pobè</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Événement</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Spectacles traditionnels de masques et danses, patrimoine immatériel UNESCO.</t>
+          <t>Chef-lieu du département du Plateau, culture yoruba-nago.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Sakété, Plateau</t>
+          <t>Pobè, Plateau</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6.7368274, 2.6636066</t>
+          <t>6.9832415, 2.6636066</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.7368274,2.6636066</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9832415,2.6636066</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Patrimoine culturel immatériel (UNESCO) ; le berceau historique documenté est plutôt Kétou/Savè.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
+          <t>Zou</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ville de Pobè</t>
+          <t>Palais royaux d'Abomey</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1568,28 +1563,44 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Chef-lieu du département du Plateau, culture yoruba-nago.</t>
+          <t>Ensemble de palais du royaume du Dahomey, classé UNESCO.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pobè, Plateau</t>
+          <t>Abomey, Zou</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6.9832415, 2.6636066</t>
+          <t>7.1855024, 1.997943</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9832415,2.6636066</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1855024,1.997943</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Tous les jours, 9h-18h</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>+229 22 50 03 14</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="21">
@@ -1599,21 +1610,21 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Palais royaux d'Abomey</t>
+          <t>Place Béhanzin (Place Goho)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Ensemble de palais du royaume du Dahomey, classé UNESCO.</t>
+          <t>Place centrale avec statue du roi Béhanzin, symbole de résistance.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1623,12 +1634,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7.1855024, 1.997943</t>
+          <t>7.1842529, 2.0078158</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1855024,1.997943</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1842529,2.0078158</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1636,35 +1647,30 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Tous les jours, 9h-18h</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>+229 22 50 03 14</t>
-        </is>
-      </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>105</v>
+        <v>5</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Un état d'entretien dégradé a été signalé par la presse locale.</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Zou</t>
+          <t>Atlantique/Zou</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Place Béhanzin (Place Goho)</t>
+          <t>Forêt classée de la Lama</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1674,83 +1680,77 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Place centrale avec statue du roi Béhanzin, symbole de résistance.</t>
+          <t>Grande forêt naturelle, observation d'animaux et de flore variée.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Abomey, Zou</t>
+          <t>Toffo, Atlantique / Zogbodomey, Zou</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7.1842529, 2.0078158</t>
+          <t>6.9179281, 2.1662158</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1842529,2.0078158</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9179281,2.1662158</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Un état d'entretien dégradé a été signalé par la presse locale.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Atlantique/Zou</t>
+          <t>Collines</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Forêt classée de la Lama</t>
+          <t>Grotte mariale de Dassa-Zoumé</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Grande forêt naturelle, observation d'animaux et de flore variée.</t>
+          <t>Lieu de pèlerinage catholique niché dans les collines.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Toffo, Atlantique / Zogbodomey, Zou</t>
+          <t>Dassa-Zoumé, Collines</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6.9179281, 2.1662158</t>
+          <t>7.7752876, 2.1865136</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9179281,2.1662158</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7752876,2.1865136</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ouvert toute l'année ; grand pèlerinage fin août</t>
         </is>
       </c>
     </row>
@@ -1761,11 +1761,11 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Grotte mariale de Dassa-Zoumé</t>
+          <t>Savalou (ville historique, culte vaudou)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1775,72 +1775,67 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Lieu de pèlerinage catholique niché dans les collines.</t>
+          <t>Ville traditionnelle marquée par la royauté locale et le culte vaudou.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Dassa-Zoumé, Collines</t>
+          <t>Savalou, Collines</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7.7752876, 2.1865136</t>
+          <t>7.9301365, 1.9710284</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7752876,2.1865136</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9301365,1.9710284</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Ouvert toute l'année ; grand pèlerinage fin août</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Collines</t>
+          <t>Mono</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Savalou (ville historique, culte vaudou)</t>
+          <t>Plage de Grand-Popo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Ville traditionnelle marquée par la royauté locale et le culte vaudou.</t>
+          <t>Plage réputée du littoral béninois, tourisme balnéaire.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Savalou, Collines</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7.9301365, 1.9710284</t>
+          <t>6.2639324, 1.7417143</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9301365,1.9710284</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2639324,1.7417143</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1856,41 +1851,51 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Plage de Grand-Popo</t>
+          <t>Village de Possotomè</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Plage réputée du littoral béninois, tourisme balnéaire.</t>
+          <t>Village au bord du lac Ahémé, source d'eau thermale.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Possotomè, Bopa, Mono</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6.2639324, 1.7417143</t>
+          <t>6.520838, 1.9625132</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2639324,1.7417143</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.520838,1.9625132</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>+229 95 28 52 20</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://www.ecobenin.org/possotome</t>
         </is>
       </c>
     </row>
@@ -1901,11 +1906,11 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Village de Possotomè</t>
+          <t>Bouche du Roy</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1915,22 +1920,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Village au bord du lac Ahémé, source d'eau thermale.</t>
+          <t>Embouchure spectaculaire entre océan, lagune et mangrove.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Possotomè, Bopa, Mono</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6.520838, 1.9625132</t>
+          <t>6.2922216, 1.917286</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.520838,1.9625132</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1940,13 +1945,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>+229 95 28 52 20</t>
+          <t>+229 60 63 08 18</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.ecobenin.org/possotome</t>
-        </is>
+          <t>https://www.boucheduroy.bj</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1956,11 +1967,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bouche du Roy</t>
+          <t>Ville de Lokossa</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1970,22 +1981,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Embouchure spectaculaire entre océan, lagune et mangrove.</t>
+          <t>Chef-lieu du département du Mono.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Lokossa, Mono</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6.2922216, 1.917286</t>
+          <t>6.6448093, 1.7198215</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.6448093,1.7198215</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1993,35 +2004,24 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>+229 60 63 08 18</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.boucheduroy.bj</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>4</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2</v>
+          <t>https://lokossa.mairie.bj/fr/decouverte</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Mono</t>
+          <t>Atacora</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Ville de Lokossa</t>
+          <t>Parc national de la Pendjari</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2031,22 +2031,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Chef-lieu du département du Mono.</t>
+          <t>Réserve faunique majeure, safaris et observation de la faune africaine.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Lokossa, Mono</t>
+          <t>Atacora</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6.6448093, 1.7198215</t>
+          <t>11.2481125, 1.5983959</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.6448093,1.7198215</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2054,9 +2054,14 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Ouvert toute l'année ; safaris recommandés 6h-11h et 16h-tombée de la nuit</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://lokossa.mairie.bj/fr/decouverte</t>
+          <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
     </row>
@@ -2067,11 +2072,11 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Parc national de la Pendjari</t>
+          <t>Villages Tata Somba</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2081,37 +2086,27 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Réserve faunique majeure, safaris et observation de la faune africaine.</t>
+          <t>Habitats traditionnels fortifiés des Batammariba.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
+          <t>Natitingou/Boukoumbé, Atacora</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11.2481125, 1.5983959</t>
+          <t>10.3091173, 1.3735244</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Ouvert toute l'année ; safaris recommandés 6h-11h et 16h-tombée de la nuit</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
     </row>
@@ -2122,36 +2117,36 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Villages Tata Somba</t>
+          <t>Cascades de Tanougou</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Habitats traditionnels fortifiés des Batammariba.</t>
+          <t>Chutes d'eau et bassins naturels dans les montagnes de l'Atacora.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Natitingou/Boukoumbé, Atacora</t>
+          <t>Tanongou, Atacora</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10.3091173, 1.3735244</t>
+          <t>10.8121477, 1.4363443</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2167,41 +2162,51 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Cascades de Tanougou</t>
+          <t>Musée régional de Natitingou</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Chutes d'eau et bassins naturels dans les montagnes de l'Atacora.</t>
+          <t>Musée sur les traditions socioculturelles de la région.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tanongou, Atacora</t>
+          <t>Natitingou, Atacora</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10.8121477, 1.4363443</t>
+          <t>10.3106873, 1.3802711</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3106873,1.3802711</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Lun-Ven 8h30-18h30, Sam-Dim 9h-18h30</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>+229 97 88 10 80</t>
         </is>
       </c>
     </row>
@@ -2212,66 +2217,56 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Musée régional de Natitingou</t>
+          <t>Chaîne de l'Atacora</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Musée sur les traditions socioculturelles de la région.</t>
+          <t>Massif montagneux, randonnée et paysages du nord-ouest du Bénin.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Natitingou, Atacora</t>
+          <t>Atacora (zone)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10.3106873, 1.3802711</t>
+          <t>10.75, 1.5</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3106873,1.3802711</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.75,1.5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Lun-Ven 8h30-18h30, Sam-Dim 9h-18h30</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>+229 97 88 10 80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
+          <t>Borgou/Donga</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Chaîne de l'Atacora</t>
+          <t>Forêt classée de Wari-Maro</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2281,67 +2276,72 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Massif montagneux, randonnée et paysages du nord-ouest du Bénin.</t>
+          <t>Réserve forestière et faunique de la région.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Atacora (zone)</t>
+          <t>Tchaourou, Borgou / Bassila, Donga</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10.75, 1.5</t>
+          <t>8.9622901, 2.1843285</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.75,1.5</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Statut en évolution : fusion annoncée avec la forêt des Monts Kouffé en un nouveau parc national (déc. gouvernementale nov. 2025).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Borgou/Donga</t>
+          <t>Donga</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Forêt classée de Wari-Maro</t>
+          <t>Village de Bassila</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Loisir</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Réserve forestière et faunique de la région.</t>
+          <t>Commune forestière du sud de la Donga.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tchaourou, Borgou / Bassila, Donga</t>
+          <t>Bassila, Donga</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8.9622901, 2.1843285</t>
+          <t>9.006393, 1.6639235</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.006393,1.6639235</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2349,24 +2349,24 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Statut en évolution : fusion annoncée avec la forêt des Monts Kouffé en un nouveau parc national (déc. gouvernementale nov. 2025).</t>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>+229 23 30 11 76</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Donga</t>
+          <t>Borgou</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Village de Bassila</t>
+          <t>Musée de plein air de Parakou</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2376,22 +2376,22 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Commune forestière du sud de la Donga.</t>
+          <t>Musée d'art et traditions populaires du nord du Bénin.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Bassila, Donga</t>
+          <t>Parakou, Borgou</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>9.006393, 1.6639235</t>
+          <t>9.3279386, 2.6174022</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.006393,1.6639235</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2399,9 +2399,19 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Tous les jours 9h-12h et 15h-18h30, sauf jours fériés</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>+229 23 30 11 76</t>
+          <t>+229 23 61 05 78</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
         </is>
       </c>
     </row>
@@ -2412,11 +2422,11 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Musée de plein air de Parakou</t>
+          <t>Palais royal de Nikki</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2426,82 +2436,67 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Musée d'art et traditions populaires du nord du Bénin.</t>
+          <t>Capitale historique des Batombu, siège royal.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Parakou, Borgou</t>
+          <t>Nikki, Borgou</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9.3279386, 2.6174022</t>
+          <t>9.9363278, 3.2105884</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9363278,3.2105884</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Tous les jours 9h-12h et 15h-18h30, sauf jours fériés</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>+229 23 61 05 78</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fête de la Gaani</t>
+          <t>Parc national du W</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Événement</t>
+          <t>Site touristique</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Grande manifestation culturelle annuelle des Batombu.</t>
+          <t>Parc transfrontalier Bénin-Niger-Burkina Faso, UNESCO.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Nikki, Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>9.9276076, 3.2167913</t>
+          <t>12.0408333, 3.0341667</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9276076,3.2167913</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2511,57 +2506,47 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3 jours fin août (ex. 25-27 août 2026)</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://gaani.bj</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Anciennement orthographié « Gani » ; deux fiches en doublon fusionnées.</t>
+          <t>Ouvert toute l'année</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Palais royal de Nikki</t>
+          <t>Fleuve Niger (rives)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Site touristique</t>
+          <t>Loisir</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Capitale historique des Batombu, siège royal.</t>
+          <t>Rives du fleuve Niger, paysages et activités fluviales.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Nikki, Borgou</t>
+          <t>Malanville, Alibori</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9.9363278, 3.2105884</t>
+          <t>11.8633332, 3.3842473</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.9363278,3.2105884</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8633332,3.3842473</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2577,11 +2562,11 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Parc national du W</t>
+          <t>Ville de Kandi</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2591,22 +2576,22 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Parc transfrontalier Bénin-Niger-Burkina Faso, UNESCO.</t>
+          <t>Chef-lieu du département de l'Alibori.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Alibori</t>
+          <t>Kandi, Alibori</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>12.0408333, 3.0341667</t>
+          <t>11.1305191, 2.9325785</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2614,104 +2599,9 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Ouvert toute l'année</t>
-        </is>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Fleuve Niger (rives)</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Loisir</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Rives du fleuve Niger, paysages et activités fluviales.</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Malanville, Alibori</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>11.8633332, 3.3842473</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8633332,3.3842473</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Ville de Kandi</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Site touristique</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Chef-lieu du département de l'Alibori.</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Kandi, Alibori</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>11.1305191, 2.9325785</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="H43" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
         </is>
@@ -2737,30 +2627,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2772,7 +2660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3419,37 +3307,37 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Atlantique</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Événement</t>
+          <t>Ouémé</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fête du Vodun (10 janvier)</t>
+          <t>Art Résidence Hôtel</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Célébration nationale du culte vaudou, grands rassemblements à Ouidah.</t>
+          <t>Hôtel boutique moderne à Porto-Novo.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Ouidah, Atlantique (chaque 10 janvier)</t>
+          <t>Porto-Novo, Ouémé</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6.3595647, 2.0851368</t>
+          <t>6.4824678, 2.6114132</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.3595647,2.0851368</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.4824678,2.6114132</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -3457,15 +3345,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Format étendu « Vodun Days » sur 2-3 jours (ex. 8-10 janvier 2026)</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://vodundays.bj</t>
-        </is>
+          <t>https://artresidence.bj</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3481,12 +3370,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Art Résidence Hôtel</t>
+          <t>Tour Eiffel Hôtel Bénin</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Hôtel boutique moderne à Porto-Novo.</t>
+          <t>Grand hôtel avec restaurant et piscine à Porto-Novo.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3496,12 +3385,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6.4824678, 2.6114132</t>
+          <t>6.4816315, 2.5956944</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.4824678,2.6114132</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.4816315,2.5956944</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -3509,16 +3398,16 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://artresidence.bj</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>+229 65 00 38 65</t>
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
         <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3527,19 +3416,19 @@
           <t>Ouémé</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tour Eiffel Hôtel Bénin</t>
+          <t>Parc d'attraction Ifè</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Grand hôtel avec restaurant et piscine à Porto-Novo.</t>
+          <t>Parc récréatif familial à Porto-Novo.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -3549,29 +3438,18 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6.4816315, 2.5956944</t>
+          <t>6.4707072, 2.6095372</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.4816315,2.5956944</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.4707072,2.6095372</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>+229 65 00 38 65</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -3587,27 +3465,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Parc d'attraction Ifè</t>
+          <t>Balade sur la Rivière Noire</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Parc récréatif familial à Porto-Novo.</t>
+          <t>Excursion en pirogue sur la Rivière Noire, village d'artisans.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Porto-Novo, Ouémé</t>
+          <t>Adjarra, Ouémé</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6.4707072, 2.6095372</t>
+          <t>6.5429012, 2.6715489</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.4707072,2.6095372</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.5429012,2.6715489</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -3629,79 +3507,79 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Balade sur la Rivière Noire</t>
+          <t>Visite du Grand Marché de Porto-Novo</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Excursion en pirogue sur la Rivière Noire, village d'artisans.</t>
+          <t>Immersion dans le grand marché local.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Adjarra, Ouémé</t>
+          <t>Porto-Novo, Ouémé</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6.5429012, 2.6715489</t>
+          <t>6.470905, 2.6266839</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.5429012,2.6715489</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.470905,2.6266839</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Marché quotidien, plus animé mercredi et samedi matin</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Ouémé</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Plateau</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Visite du Grand Marché de Porto-Novo</t>
+          <t>Adebayo Hôtel</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Immersion dans le grand marché local.</t>
+          <t>Hôtel avec restaurant, l'un des mieux notés de Pobè.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Porto-Novo, Ouémé</t>
+          <t>Pobè, Plateau</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6.470905, 2.6266839</t>
+          <t>6.9774796, 2.658367</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.470905,2.6266839</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9774796,2.658367</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Marché quotidien, plus animé mercredi et samedi matin</t>
         </is>
       </c>
     </row>
@@ -3711,39 +3589,44 @@
           <t>Plateau</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Adebayo Hôtel</t>
+          <t>Visite du musée Akaba Idena</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Hôtel avec restaurant, l'un des mieux notés de Pobè.</t>
+          <t>Découverte de l'histoire de Kétou et des portes magiques.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Pobè, Plateau</t>
+          <t>Kétou, Plateau</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6.9774796, 2.658367</t>
+          <t>7.3634919, 2.6016927</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9774796,2.658367</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.3634919,2.6016927</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
         </is>
       </c>
     </row>
@@ -3760,12 +3643,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Visite du musée Akaba Idena</t>
+          <t>Balade dans la cité royale de Kétou</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Découverte de l'histoire de Kétou et des portes magiques.</t>
+          <t>Immersion dans l'histoire yoruba-nago.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -3775,59 +3658,54 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7.3634919, 2.6016927</t>
+          <t>7.3603376, 2.6040436</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.3634919,2.6016927</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.3603376,2.6040436</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Zou</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Balade dans la cité royale de Kétou</t>
+          <t>Ekagnon Hôtel Abomey</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Immersion dans l'histoire yoruba-nago.</t>
+          <t>Hôtel haut de gamme, l'un des mieux notés d'Abomey.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Kétou, Plateau</t>
+          <t>Abomey, Zou</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7.3603376, 2.6040436</t>
+          <t>7.1640097, 2.0021363</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.3603376,2.6040436</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1640097,2.0021363</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3839,43 +3717,54 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Plateau</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Événement</t>
+          <t>Zou</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Guèlèdè (spectacle de masques)</t>
+          <t>Bois Vert Hôtel</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Spectacle traditionnel de masques et danses, patrimoine UNESCO, Kétou/Sakété.</t>
+          <t>Hôtel confortable proche du centre d'Abomey.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kétou/Sakété, Plateau</t>
+          <t>Abomey, Zou</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6.7368274, 2.6636066</t>
+          <t>7.1732015, 1.9902517</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.7368274,2.6636066</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1732015,1.9902517</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>+229 01 55 40 98 78</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3891,12 +3780,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ekagnon Hôtel Abomey</t>
+          <t>Chez Sabine</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Hôtel haut de gamme, l'un des mieux notés d'Abomey.</t>
+          <t>Maison d'hôtes chaleureuse à Abomey.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3906,18 +3795,29 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7.1640097, 2.0021363</t>
+          <t>7.183616, 2.0302333</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1640097,2.0021363</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.183616,2.0302333</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>+229 63 13 64 64</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -3926,19 +3826,19 @@
           <t>Zou</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bois Vert Hôtel</t>
+          <t>Visite guidée des palais royaux (Guide Abomey)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable proche du centre d'Abomey.</t>
+          <t>Guide local pour explorer l'histoire du royaume du Dahomey.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3948,12 +3848,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7.1732015, 1.9902517</t>
+          <t>7.1889261, 1.9942085</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1732015,1.9902517</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1889261,1.9942085</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3961,105 +3861,94 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>+229 01 55 40 98 78</t>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9h-18h (une source indique 8h-17h)</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Zou</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+          <t>Atlantique/Zou</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Chez Sabine</t>
+          <t>Découverte de la Forêt classée de la Lama</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Maison d'hôtes chaleureuse à Abomey.</t>
+          <t>Observation de la faune et de la flore.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Abomey, Zou</t>
+          <t>Toffo, Atlantique / Zogbodomey, Zou</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7.183616, 2.0302333</t>
+          <t>6.9179281, 2.1662158</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.183616,2.0302333</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9179281,2.1662158</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>+229 63 13 64 64</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M25" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Zou</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Collines</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Visite guidée des palais royaux (Guide Abomey)</t>
+          <t>Hôtel Jeco</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Guide local pour explorer l'histoire du royaume du Dahomey.</t>
+          <t>Hôtel confortable avec piscine à Dassa-Zoumé.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Abomey, Zou</t>
+          <t>Dassa-Zoumé, Collines</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7.1889261, 1.9942085</t>
+          <t>7.7790481, 2.1843505</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.1889261,1.9942085</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7790481,2.1843505</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -4067,58 +3956,74 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>9h-18h (une source indique 8h-17h)</t>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>+229 22 53 08 89</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://jecohotels.com</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Atlantique/Zou</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Collines</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Découverte de la Forêt classée de la Lama</t>
+          <t>Auberge de Dassa-Zoumé</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Observation de la faune et de la flore.</t>
+          <t>Auberge bien située, halte pratique sur la route du nord.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Toffo, Atlantique / Zogbodomey, Zou</t>
+          <t>Dassa-Zoumé, Collines</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6.9179281, 2.1662158</t>
+          <t>7.7811209, 2.1824554</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.9179281,2.1662158</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7811209,2.1824554</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>+229 94 47 21 35</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -4134,27 +4039,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Jeco</t>
+          <t>Loubna Hôtel &amp; Restauration</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable avec piscine à Dassa-Zoumé.</t>
+          <t>Hôtel confortable à Paouignan, près des collines.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Dassa-Zoumé, Collines</t>
+          <t>Paouignan, Collines</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7.7790481, 2.1843505</t>
+          <t>7.6698299, 2.2237021</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7790481,2.1843505</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.6698299,2.2237021</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -4162,21 +4067,15 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>+229 22 53 08 89</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://jecohotels.com</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M28" t="n">
-        <v>43</v>
+          <t>https://loubna-hotel.com</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Référencé en ligne sous le nom « Hôtel Loubna Évolution ».</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -4185,19 +4084,19 @@
           <t>Collines</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Auberge de Dassa-Zoumé</t>
+          <t>Pèlerinage à la Grotte mariale de Dassa</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Auberge bien située, halte pratique sur la route du nord.</t>
+          <t>Visite du site de pèlerinage catholique niché dans les collines.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4207,12 +4106,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7.7811209, 2.1824554</t>
+          <t>7.7752876, 2.1865136</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7811209,2.1824554</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7752876,2.1865136</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4220,16 +4119,10 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>+229 94 47 21 35</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>12</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Site ouvert toute l'année ; pèlerinage vers le 15 août</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -4238,49 +4131,39 @@
           <t>Collines</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Loubna Hôtel &amp; Restauration</t>
+          <t>Visite du sanctuaire vaudou de Dankoli</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable à Paouignan, près des collines.</t>
+          <t>Découverte d'un des sanctuaires vaudou les plus actifs d'Afrique de l'Ouest.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Paouignan, Collines</t>
+          <t>Savalou, Collines</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7.6698299, 2.2237021</t>
+          <t>7.9301365, 1.9710284</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.6698299,2.2237021</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9301365,1.9710284</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>https://loubna-hotel.com</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Référencé en ligne sous le nom « Hôtel Loubna Évolution ».</t>
         </is>
       </c>
     </row>
@@ -4297,116 +4180,127 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Pèlerinage à la Grotte mariale de Dassa</t>
+          <t>Visite du Palais Royal de Savalou</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Visite du site de pèlerinage catholique niché dans les collines.</t>
+          <t>Immersion dans l'histoire du royaume Mahi.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Dassa-Zoumé, Collines</t>
+          <t>Savalou, Collines</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7.7752876, 2.1865136</t>
+          <t>7.9313702, 1.9726773</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.7752876,2.1865136</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9313702,1.9726773</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Site ouvert toute l'année ; pèlerinage vers le 15 août</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Collines</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Mono</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Visite du sanctuaire vaudou de Dankoli</t>
+          <t>Awale Plage</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Découverte d'un des sanctuaires vaudou les plus actifs d'Afrique de l'Ouest.</t>
+          <t>Hôtel-restaurant en bord de plage à Grand-Popo.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Savalou, Collines</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7.9301365, 1.9710284</t>
+          <t>6.270213, 1.786942</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9301365,1.9710284</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.270213,1.786942</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>+229 58 01 01 12</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://www.hotel-benin-awaleplage.com</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M32" t="n">
+        <v>137</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Collines</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Mono</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Visite du Palais Royal de Savalou</t>
+          <t>ASVA Beach Resort</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Immersion dans l'histoire du royaume Mahi.</t>
+          <t>Hôtel proche de la plage, ambiance festive.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Savalou, Collines</t>
+          <t>Grand-Popo, Mono</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7.9313702, 1.9726773</t>
+          <t>6.2757733, 1.8104271</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=7.9313702,1.9726773</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2757733,1.8104271</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4428,12 +4322,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Awale Plage</t>
+          <t>Millenium Popo Beach Hôtel</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Hôtel-restaurant en bord de plage à Grand-Popo.</t>
+          <t>Grand complexe hôtelier en bord de mer.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4443,12 +4337,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6.270213, 1.786942</t>
+          <t>6.2518431, 1.6979677</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.270213,1.786942</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2518431,1.6979677</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4458,19 +4352,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>+229 58 01 01 12</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>https://www.hotel-benin-awaleplage.com</t>
+          <t>+229 6860 1111</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>137</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -4479,19 +4368,19 @@
           <t>Mono</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ASVA Beach Resort</t>
+          <t>Excursions avec BAKOLO Tours</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Hôtel proche de la plage, ambiance festive.</t>
+          <t>Agence locale pour circuits sur mesure dans la région.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4501,17 +4390,27 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6.2757733, 1.8104271</t>
+          <t>6.2772786, 1.8037903</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2757733,1.8104271</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2772786,1.8037903</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>+229 94 69 96 89</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://www.bakolotours.com</t>
         </is>
       </c>
     </row>
@@ -4521,19 +4420,19 @@
           <t>Mono</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Millenium Popo Beach Hôtel</t>
+          <t>Sortie bateau vers la Bouche du Roy</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Grand complexe hôtelier en bord de mer.</t>
+          <t>Excursion vers l'embouchure entre océan et lagune.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4543,65 +4442,54 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6.2518431, 1.6979677</t>
+          <t>6.2922216, 1.917286</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2518431,1.6979677</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>+229 6860 1111</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Mono</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Atacora</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Excursions avec BAKOLO Tours</t>
+          <t>Hôtel Bellevue</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Agence locale pour circuits sur mesure dans la région.</t>
+          <t>Hôtel historique et chaleureux à Natitingou.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Natitingou, Atacora</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6.2772786, 1.8037903</t>
+          <t>10.3059893, 1.3856433</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2772786,1.8037903</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3059893,1.3856433</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4611,55 +4499,62 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>+229 94 69 96 89</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>https://www.bakolotours.com</t>
-        </is>
+          <t>+229 23 82 13 36</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Mono</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Atacora</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Sortie bateau vers la Bouche du Roy</t>
+          <t>Hôtel Tata Somba</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Excursion vers l'embouchure entre océan et lagune.</t>
+          <t>Hôtel au pied des collines, proche des villages Tata Somba.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Grand-Popo, Mono</t>
+          <t>Natitingou, Atacora</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6.2922216, 1.917286</t>
+          <t>10.3091173, 1.3735244</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=6.2922216,1.917286</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="L38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="39">
@@ -4675,12 +4570,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Bellevue</t>
+          <t>Hôtel Totora</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Hôtel historique et chaleureux à Natitingou.</t>
+          <t>Hôtel avec piscine et vue sur les montagnes.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4690,12 +4585,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10.3059893, 1.3856433</t>
+          <t>10.3181651, 1.3738271</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3059893,1.3856433</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3181651,1.3738271</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4705,14 +4600,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+229 23 82 13 36</t>
+          <t>+229 62 23 62 52</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.hoteltotora.com</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>20</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40">
@@ -4721,34 +4621,34 @@
           <t>Atacora</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Tata Somba</t>
+          <t>Safari au Parc national de la Pendjari</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Hôtel au pied des collines, proche des villages Tata Somba.</t>
+          <t>Safari guidé pour observer lions, éléphants, hippopotames.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Natitingou, Atacora</t>
+          <t>Atacora</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10.3091173, 1.3735244</t>
+          <t>11.2481125, 1.5983959</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4756,11 +4656,15 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M40" t="n">
-        <v>217</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.african-parks.org/the-parks/pendjari</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -4769,56 +4673,40 @@
           <t>Atacora</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Totora</t>
+          <t>Visite des villages Tata Somba</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Hôtel avec piscine et vue sur les montagnes.</t>
+          <t>Découverte des habitats fortifiés traditionnels.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Natitingou, Atacora</t>
+          <t>Natitingou/Boukoumbé, Atacora</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10.3181651, 1.3738271</t>
+          <t>10.3091173, 1.3735244</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3181651,1.3738271</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>+229 62 23 62 52</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://www.hoteltotora.com</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>375</v>
       </c>
     </row>
     <row r="42">
@@ -4834,127 +4722,133 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Safari au Parc national de la Pendjari</t>
+          <t>Randonnée aux cascades de Tanougou</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Safari guidé pour observer lions, éléphants, hippopotames.</t>
+          <t>Baignade et randonnée dans un cadre naturel.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
+          <t>Tanongou, Atacora</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11.2481125, 1.5983959</t>
+          <t>10.8121477, 1.4363443</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.2481125,1.5983959</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Donga</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Visite des villages Tata Somba</t>
+          <t>Motel Du Lac</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Découverte des habitats fortifiés traditionnels.</t>
+          <t>Hôtel familial réputé pour sa cuisine, à Djougou.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Natitingou/Boukoumbé, Atacora</t>
+          <t>Djougou, Donga</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10.3091173, 1.3735244</t>
+          <t>9.6802129, 1.6527047</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3091173,1.3735244</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6802129,1.6527047</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>+229 97 54 06 56</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Atacora</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Donga</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Randonnée aux cascades de Tanougou</t>
+          <t>Hôtel de la Donga</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Baignade et randonnée dans un cadre naturel.</t>
+          <t>Hôtel simple et pratique à Djougou.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tanongou, Atacora</t>
+          <t>Djougou, Donga</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10.8121477, 1.4363443</t>
+          <t>9.6997379, 1.6732916</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.8121477,1.4363443</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6997379,1.6732916</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>+229 23 80 15 72</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -4970,12 +4864,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Motel Du Lac</t>
+          <t>Hôtel Cathas</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Hôtel familial réputé pour sa cuisine, à Djougou.</t>
+          <t>Hôtel accessible au centre de Djougou.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4985,12 +4879,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>9.6802129, 1.6527047</t>
+          <t>9.6989611, 1.6729295</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6802129,1.6527047</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6989611,1.6729295</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5000,67 +4894,56 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>+229 97 54 06 56</t>
+          <t>+229 66 03 37 51</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Donga</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+          <t>Borgou/Donga</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Hôtel de la Donga</t>
+          <t>Découverte de la Forêt classée de Wari-Maro</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Hôtel simple et pratique à Djougou.</t>
+          <t>Randonnée nature et observation de la faune.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Djougou, Donga</t>
+          <t>Tchaourou, Borgou / Bassila, Donga</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9.6997379, 1.6732916</t>
+          <t>8.9622901, 2.1843285</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6997379,1.6732916</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>+229 23 80 15 72</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>3</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Donga</t>
+          <t>Borgou</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -5070,80 +4953,81 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Cathas</t>
+          <t>Ola Luxury Hôtel</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Hôtel accessible au centre de Djougou.</t>
+          <t>Hôtel confortable et bien noté à Parakou.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Djougou, Donga</t>
+          <t>Parakou, Borgou</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9.6989611, 1.6729295</t>
+          <t>9.3553016, 2.6330228</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.6989611,1.6729295</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3553016,2.6330228</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>+229 66 03 37 51</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Borgou/Donga</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
+          <t>Borgou</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Découverte de la Forêt classée de Wari-Maro</t>
+          <t>Kobourou City Hôtel</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Randonnée nature et observation de la faune.</t>
+          <t>Grand hôtel avec piscine à Parakou.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Tchaourou, Borgou / Bassila, Donga</t>
+          <t>Parakou, Borgou</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>8.9622901, 2.1843285</t>
+          <t>9.3664096, 2.6247833</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=8.9622901,2.1843285</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3664096,2.6247833</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -5159,12 +5043,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Ola Luxury Hôtel</t>
+          <t>Hôtel Iya-Oasis</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable et bien noté à Parakou.</t>
+          <t>Hôtel au décor traditionnel, très bien noté à Parakou.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5174,18 +5058,24 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>9.3553016, 2.6330228</t>
+          <t>9.3457835, 2.6373219</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3553016,2.6330228</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3457835,2.6373219</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
+      </c>
+      <c r="L49" t="n">
+        <v>5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -5194,19 +5084,19 @@
           <t>Borgou</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Activité</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Kobourou City Hôtel</t>
+          <t>Visite du musée de plein air de Parakou</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Grand hôtel avec piscine à Parakou.</t>
+          <t>Découverte de l'art et des traditions du nord du Bénin.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5216,12 +5106,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9.3664096, 2.6247833</t>
+          <t>9.3279386, 2.6174022</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3664096,2.6247833</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5229,17 +5119,26 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
-      <c r="L50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M50" t="n">
-        <v>6</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Tous les jours 9h-12h et 15h-18h30, sauf jours fériés</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>+229 23 61 05 78</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -5249,45 +5148,39 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Hôtel Iya-Oasis</t>
+          <t>Hôtel Séjour du Sahel</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Hôtel au décor traditionnel, très bien noté à Parakou.</t>
+          <t>Hôtel propre et sécurisé à Malanville.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Parakou, Borgou</t>
+          <t>Malanville, Alibori</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>9.3457835, 2.6373219</t>
+          <t>11.8523034, 3.389122</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3457835,2.6373219</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8523034,3.389122</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
         </is>
-      </c>
-      <c r="L51" t="n">
-        <v>5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -5297,27 +5190,27 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Visite du musée de plein air de Parakou</t>
+          <t>Safari au Parc national du W</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Découverte de l'art et des traditions du nord du Bénin.</t>
+          <t>Observation de la faune dans le parc transfrontalier UNESCO.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Parakou, Borgou</t>
+          <t>Alibori</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9.3279386, 2.6174022</t>
+          <t>12.0408333, 3.0341667</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=9.3279386,2.6174022</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -5327,118 +5220,19 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Tous les jours 9h-12h et 15h-18h30, sauf jours fériés</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>+229 23 61 05 78</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
+          <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Hôtel</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Hôtel Séjour du Sahel</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Hôtel propre et sécurisé à Malanville.</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Malanville, Alibori</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>11.8523034, 3.389122</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=11.8523034,3.389122</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>Activité</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Safari au Parc national du W</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Observation de la faune dans le parc transfrontalier UNESCO.</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Alibori</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>12.0408333, 3.0341667</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8523034,3.389122</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="G56" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
         </is>
@@ -5458,48 +5252,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="60 Lieux incontournables" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hôtels-Activités-Événements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="60 Lieux incontournables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hôtels-Activités-Événements" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'60 Lieux incontournables'!$A$1:$I$43</definedName>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,36 @@
           <t>Remarque</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Prix</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Gamme de prix</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Durée</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Ambiances</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Idéal pour</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Infos estimées</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -624,6 +654,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Entrée libre (lieu de culte)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>spiritualite, culture</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -690,6 +750,36 @@
       <c r="N3" t="n">
         <v>88</v>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Entrée gratuite</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>art, culture</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -741,6 +831,36 @@
       <c r="N4" t="n">
         <v>72</v>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Accès libre</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>plage, detente</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -792,6 +912,36 @@
       <c r="N5" t="n">
         <v>15</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Accès libre (espace public)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -848,6 +998,31 @@
       <c r="N6" t="n">
         <v>15</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>amis, famille</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -904,6 +1079,36 @@
       <c r="N7" t="n">
         <v>5</v>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Parcours en accès libre ; guide en option</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -965,6 +1170,36 @@
       <c r="N8" t="n">
         <v>142</v>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>≈ 2 000 FCFA / pers. (tarif relevé en 2021)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>spiritualite, culture</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1016,6 +1251,36 @@
       <c r="N9" t="n">
         <v>10</v>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>≈ 1 100 FCFA / pers. (tarif relevé en 2021)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>spiritualite, nature, culture</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1077,6 +1342,36 @@
           <t>Possiblement fermé pour rénovation depuis 2026 — vérifier avant de s'y rendre.</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>≈ 5 000 FCFA / pers. pour le musée d'histoire (tarif 2021, fermeture possible)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1128,6 +1423,36 @@
       <c r="N11" t="n">
         <v>69</v>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>≈ 5 000 à 10 500 FCFA / pers. (pirogue + guide, selon taille du groupe)</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>culture, aventure</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1179,6 +1504,36 @@
       <c r="N12" t="n">
         <v>21</v>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>≈ 1 000 FCFA / pers.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1235,6 +1590,31 @@
       <c r="N13" t="n">
         <v>21</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>histoire, culture, art</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1291,6 +1671,31 @@
       <c r="N14" t="n">
         <v>29</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>culture, art</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1351,6 +1756,36 @@
           <t>https://songhai.org</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Visite guidée d'environ 1 h ; restaurant sur place (≈ 1 200 à 3 500 FCFA le plat)</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>nature, culture</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1401,6 +1836,36 @@
           <t>Messes semaine 6h, 12h45, 18h ; dimanche 7h, 9h, 10h30, 19h</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Entrée libre (lieu de culte)</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>spiritualite, histoire</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1446,6 +1911,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1496,6 +1986,31 @@
           <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1541,6 +2056,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Découverte libre de la ville</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1602,6 +2147,36 @@
       <c r="N20" t="n">
         <v>105</v>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>≈ 3 000 à 5 000 FCFA / pers.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1658,6 +2233,36 @@
           <t>Un état d'entretien dégradé a été signalé par la presse locale.</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Accès libre (espace public)</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>histoire</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1703,6 +2308,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>nature, faune, aventure</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>amis, famille</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1753,6 +2383,36 @@
           <t>Ouvert toute l'année ; grand pèlerinage fin août</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Accès libre (lieu de pèlerinage)</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>spiritualite, nature</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1798,6 +2458,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>culture, spiritualite, histoire</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1843,6 +2528,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Accès libre</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>plage, detente</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1898,6 +2613,31 @@
           <t>https://www.ecobenin.org/possotome</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>nature, detente, culture</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1959,6 +2699,36 @@
       <c r="N27" t="n">
         <v>2</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>≈ 10 000 FCFA / pers. en pirogue (réductions possibles en groupe)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>nature, aventure, plage</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2009,6 +2779,36 @@
           <t>https://lokossa.mairie.bj/fr/decouverte</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Découverte libre de la ville</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2064,6 +2864,36 @@
           <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Entrée ≈ 19 € adulte étranger, ≈ 7 € résident béninois (anciens tarifs), + véhicule et guide</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>eleve</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>faune, nature, aventure</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2109,6 +2939,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>culture, histoire</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2154,6 +3009,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>nature, aventure, detente</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2209,6 +3089,31 @@
           <t>+229 97 88 10 80</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>culture, histoire</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2254,6 +3159,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Accès libre ; guide conseillé pour la randonnée</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>nature, aventure, sport</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>solo, amis</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2304,6 +3239,31 @@
           <t>Statut en évolution : fusion annoncée avec la forêt des Monts Kouffé en un nouveau parc national (déc. gouvernementale nov. 2025).</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>nature, faune, aventure</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>amis</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2354,6 +3314,36 @@
           <t>+229 23 30 11 76</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Découverte libre</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>nature, culture</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>solo, amis</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2414,6 +3404,31 @@
           <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>culture, art</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2459,6 +3474,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2509,6 +3549,36 @@
           <t>Ouvert toute l'année</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Entrée ≈ 10 000 FCFA / 24 h, + véhicule (≈ 60 000 à 70 000 FCFA), guide (≈ 20 000 FCFA) et carburant</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>eleve</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>faune, nature, aventure</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2554,6 +3624,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Accès libre ; balade en pirogue à négocier sur place</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>nature, detente</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2599,9 +3699,53 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Découverte libre de la ville</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>solo, amis</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8633332,3.3842473</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=11.1305191,2.9325785</t>
         </is>
@@ -2660,7 +3804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2744,6 +3888,36 @@
           <t>Remarque</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Prix</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Gamme de prix</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Durée</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Ambiances</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Idéal pour</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Infos estimées</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2796,6 +3970,36 @@
           <t>https://www.beachsandhotel.com</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Dès ≈ 33 USD / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>detente, plage</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>couple, famille</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2844,6 +4048,36 @@
       <c r="M3" t="n">
         <v>8</v>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Dès ≈ 36 € / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2907,6 +4141,36 @@
           <t>Notes très divergentes selon la plateforme (2/5 TripAdvisor vs retours positifs ailleurs).</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Dès ≈ 30 USD / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>plage, detente</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2959,6 +4223,31 @@
           <t>https://sites.google.com/view/aquamazone229/accueil</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>sport, aventure, plage</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>amis, famille</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3001,6 +4290,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Balade libre (transport à prévoir)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>plage, detente, nature</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3043,6 +4362,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3095,6 +4439,36 @@
           <t>https://nativehotels.net</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Dès ≈ 127 £ / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eleve</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>detente, histoire</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>couple</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3147,6 +4521,31 @@
           <t>Localisation précise : Kpomassè, lac Ahémé (à ~20 min de Ouidah)</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>detente, nature</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>couple, famille</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3194,6 +4593,31 @@
           <t>Tous les jours 9h-22h</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>loisirs</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>amis, famille</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3251,6 +4675,31 @@
           <t>https://nadalevasiontours.com</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>histoire, culture, spiritualite</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3303,6 +4752,36 @@
           <t>https://www.visit-ganvie-tourism.com</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>≈ 5 000 à 10 500 FCFA / pers. (pirogue + guide, selon taille du groupe)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>culture, aventure</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3356,6 +4835,36 @@
       <c r="M13" t="n">
         <v>1</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Dès ≈ 150 USD / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eleve</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>detente, art</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>couple</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3409,6 +4918,36 @@
       <c r="M14" t="n">
         <v>5</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Dès ≈ 44 USD / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3451,6 +4990,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>loisirs</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>amis, famille</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3493,6 +5057,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>nature, aventure, culture</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3540,6 +5129,36 @@
           <t>Marché quotidien, plus animé mercredi et samedi matin</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Entrée libre (achats en sus)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>marche, culture</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3582,6 +5201,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3629,6 +5273,31 @@
           <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3671,6 +5340,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3713,6 +5407,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>couple, famille</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3766,6 +5485,31 @@
       <c r="M22" t="n">
         <v>3</v>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3819,6 +5563,36 @@
       <c r="M23" t="n">
         <v>30</v>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>≈ 34 à 73 USD / nuit pour 2 adultes (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>detente, culture</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3872,6 +5646,36 @@
       <c r="M24" t="n">
         <v>105</v>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Entrée du site ≈ 3 000 à 5 000 FCFA / pers., guide en sus</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3914,6 +5718,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>nature, faune, aventure</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>amis, famille</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3972,6 +5801,31 @@
       <c r="M26" t="n">
         <v>43</v>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>couple, famille</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4025,6 +5879,31 @@
       <c r="M27" t="n">
         <v>12</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>solo, amis</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4077,6 +5956,31 @@
           <t>Référencé en ligne sous le nom « Hôtel Loubna Évolution ».</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4124,6 +6028,36 @@
           <t>Site ouvert toute l'année ; pèlerinage vers le 15 août</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Accès libre (lieu de pèlerinage)</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>gratuit</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>spiritualite, nature</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4166,6 +6100,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>spiritualite, culture</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>solo, couple, amis</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4208,6 +6167,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>histoire, culture</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4266,6 +6250,36 @@
       <c r="M32" t="n">
         <v>137</v>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Dès ≈ 29 USD / nuit (plateformes de réservation)</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>plage, detente</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4308,6 +6322,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>plage, detente</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>amis, couple</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4361,6 +6400,31 @@
       <c r="M34" t="n">
         <v>16</v>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>plage, detente</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>couple, famille</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4413,6 +6477,31 @@
           <t>https://www.bakolotours.com</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>nature, culture, aventure</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4455,6 +6544,36 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>≈ 10 000 FCFA / pers. (réductions possibles en groupe)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>nature, aventure, plage</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4508,6 +6627,31 @@
       <c r="M37" t="n">
         <v>20</v>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4556,6 +6700,31 @@
       <c r="M38" t="n">
         <v>217</v>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>detente, culture</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4614,6 +6783,31 @@
       <c r="M39" t="n">
         <v>375</v>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>detente, nature</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>couple, famille</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4666,6 +6860,36 @@
           <t>https://www.african-parks.org/the-parks/pendjari</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Entrée ≈ 19 € adulte étranger, ≈ 7 € résident béninois (anciens tarifs), + véhicule et guide</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>eleve</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>faune, nature, aventure</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4708,6 +6932,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>culture, histoire</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4750,6 +6999,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>demi_journee</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>nature, aventure, detente</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4797,6 +7071,31 @@
           <t>+229 97 54 06 56</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>solo, famille</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4850,6 +7149,31 @@
       <c r="M44" t="n">
         <v>5</v>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4897,6 +7221,31 @@
           <t>+229 66 03 37 51</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4939,6 +7288,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>journee</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>nature, faune, aventure</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>amis</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4981,6 +7355,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5029,6 +7428,31 @@
       <c r="M48" t="n">
         <v>6</v>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>solo, couple, famille</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5077,6 +7501,31 @@
       <c r="M49" t="n">
         <v>5</v>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>moyen</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>detente, culture</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>solo, couple</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5134,6 +7583,31 @@
           <t>https://tourisme.parakou.bj/2024/01/18/musee-plein-air-et-ethnographique/</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>courte</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>culture, art</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>solo, couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5176,6 +7650,31 @@
           <t>Vérifié (Google Places)</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>economique</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>detente</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5223,6 +7722,36 @@
           <t>Créneaux recommandés 6h-11h et 16h-tombée de la nuit</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Entrée ≈ 10 000 FCFA / 24 h, + véhicule (≈ 60 000 à 70 000 FCFA), guide (≈ 20 000 FCFA) et carburant</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>eleve</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>sejour</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>faune, nature, aventure</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>couple, amis, famille</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="G53" t="inlineStr">
@@ -5233,6 +7762,20 @@
     </row>
     <row r="54">
       <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=11.8523034,3.389122</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=12.0408333,3.0341667</t>
         </is>

--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>demi_journee</t>
+          <t>courte</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">

--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -609,6 +609,11 @@
           <t>Infos estimées</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Alerte</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -631,7 +636,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Paroisse et lieu de culte emblématique de Cotonou, repère du quartier Sainte Rita.</t>
+          <t>Au cœur du quartier qui porte son nom, l'église Sainte-Rita est l'un des repères les plus connus de Cotonou. On y passe pour une messe, un moment de calme ou simplement pour voir l'animation du carrefour voisin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -706,7 +711,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Espace d'art contemporain africain, expositions temporaires et médiathèque.</t>
+          <t>Créée en 2005 par Marie-Cécile Zinsou, la fondation a fait de l'art contemporain africain une sortie gratuite et accessible à tous. Expositions temporaires, médiathèque et ateliers pour enfants : une adresse culturelle incontournable de Cotonou.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -802,7 +807,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Plage populaire de Cotonou, accès libre, idéale pour la détente en bord de mer.</t>
+          <t>La plage des Cotonois : sable clair, maquis et paillotes les pieds dans le sable, ambiance animée le week-end. Idéale pour une fin d'après-midi face à l'océan — la baignade y est dangereuse à cause des courants, on profite plutôt du rivage.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -883,7 +888,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ancienne Place des Martyrs, site mémoriel dédié à l'indépendance du Bénin.</t>
+          <t>Inaugurée en 2022, la statue de l'Amazone culmine à près de 30 mètres et rend hommage aux guerrières du royaume du Dahomey. L'esplanade de la Place du Souvenir se prête à une courte visite, idéalement au coucher du soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -964,7 +969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Principal stade national, matchs de football et grands événements.</t>
+          <t>Le stade Général Mathieu Kérékou, ex-stade de l'Amitié, accueille jusqu'à 35 000 spectateurs. C'est ici que vibrent les grands matchs des Guépards du Bénin et les rassemblements populaires de Cotonou.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1045,7 +1050,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chemin mémoriel de la traite négrière menant à la Porte du Non-Retour.</t>
+          <t>Un peu plus de trois kilomètres entre la place des enchères et la plage : la Route des Esclaves retrace le dernier chemin des captifs déportés vers les Amériques. L'arbre de l'Oubli, le mémorial de Zoungbodji et la Porte du Non-Retour, érigée en 1995, en marquent les étapes.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1131,7 +1136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Temple vaudou dédié aux pythons royaux, symboles sacrés.</t>
+          <t>Face à la basilique de l'Immaculée Conception, ce sanctuaire vaudou dédié à Dangbé, le dieu python, abrite des dizaines de pythons royaux. Les guides racontent la place de ces serpents sacrés dans l'histoire de Ouidah — les plus téméraires les portent autour du cou.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Forêt sacrée liée à la mythologie vaudou et au fondateur de Ouidah.</t>
+          <t>Selon la tradition, le roi Kpassè, fondateur de Ouidah, s'y serait changé en iroko pour échapper à ses ennemis. Sous les grands arbres, des sculptures de divinités vaudou installées pour le festival de 1993 jalonnent une balade paisible en plein centre-ville.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1303,7 +1308,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Ancien comptoir colonial portugais, vestige historique.</t>
+          <t>Construit en 1721, l'ancien fort portugais abrite le musée d'histoire de Ouidah et ses quelque 700 objets sur la traite et les liens entre le Bénin, le Brésil et les Caraïbes. Vérifiez l'ouverture avant de vous déplacer : le site a été annoncé en rénovation.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1337,11 +1342,6 @@
       <c r="N10" t="n">
         <v>79</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Possiblement fermé pour rénovation depuis 2026 — vérifier avant de s'y rendre.</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>≈ 5 000 FCFA / pers. pour le musée d'histoire (tarif 2021, fermeture possible)</t>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Village lacustre sur pilotis, surnommé la Venise de l'Afrique.</t>
+          <t>Plus grand village lacustre d'Afrique, Ganvié s'est bâti sur pilotis au milieu du lac Nokoué, où les Tofinu se réfugièrent pour échapper aux razzias esclavagistes. On le découvre en pirogue, entre maisons sur l'eau, marché flottant et techniques de pêche ancestrales.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ancien palais du roi Toffa, aujourd'hui musée d'histoire.</t>
+          <t>Le musée Honmè occupe le palais du roi Toffa, qui signa le protectorat avec la France en 1883. Les pièces conservées dans leur état d'origine racontent la vie de cour du royaume de Hogbonou, ancêtre de Porto-Novo.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Musée sur l'histoire afro-brésilienne et la traite négrière.</t>
+          <t>Installé dans une belle demeure afro-brésilienne de 1870, le musée da Silva retrace l'histoire des Agudas, ces anciens esclaves revenus du Brésil. Mobilier d'époque et photos anciennes font revivre l'architecture et le métissage culturel de Porto-Novo.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Collections culturelles et traditionnelles béninoises.</t>
+          <t>Fondé en 1957 dans une maison coloniale, le musée Adandé réunit masques guèlèdè, statuettes et objets rituels venus de tout le pays. Une introduction claire à la diversité des cultures béninoises, avant de partir les découvrir sur le terrain.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Centre agro-écologique reconnu, visites pédagogiques.</t>
+          <t>Fondé en 1985 par le père Godfrey Nzamujo, Songhaï est devenu une référence de l'agriculture intégrée en Afrique : « rien ne se perd, tout se transforme ». La visite guidée d'une heure parcourt cultures, élevages et ateliers, avant une pause au restaurant ou à la boutique de produits maison.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Cathédrale de l'Immaculée Conception, édifice religieux historique.</t>
+          <t>La cathédrale Notre-Dame-de-l'Immaculée-Conception affiche une façade colorée inspirée de l'architecture afro-brésilienne du vieux Porto-Novo. Un arrêt rapide pendant une balade dans le centre historique de la capitale.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Ancienne cité yoruba, berceau du Guèlèdè (patrimoine UNESCO).</t>
+          <t>Kétou, cité yoruba fondée au XIVe siècle, est le berceau du Guèlèdè, inscrit au patrimoine immatériel de l'UNESCO. On y découvre la cour royale, les remparts de terre et la célèbre porte Akaba Idéna.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Musée dédié à l'histoire et aux traditions de Kétou.</t>
+          <t>Akaba Idéna, la « porte magique », gardait l'entrée de Kétou ; reconstruite en 1894 après la destruction de la ville par le royaume d'Abomey, elle abrite des autels des divinités yoruba. Le site est en travaux de réhabilitation : renseignez-vous avant de vous déplacer.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1979,11 +1979,6 @@
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2033,7 +2028,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Chef-lieu du département du Plateau, culture yoruba-nago.</t>
+          <t>Chef-lieu du Plateau, Pobè vit au rythme de la culture yoruba-nago et des palmeraies qui l'entourent. Une étape authentique, loin des circuits classiques, pour qui explore l'est du pays.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2108,7 +2103,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Ensemble de palais du royaume du Dahomey, classé UNESCO.</t>
+          <t>Douze rois du Dahomey se sont succédé ici de 1625 à 1900, chacun bâtissant son propre palais. Classé à l'UNESCO depuis 1985, le site dévoile ses bas-reliefs, trônes et récits de la cour, avec les palais restaurés de Ghézo et de Glèlè.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2199,7 +2194,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Place centrale avec statue du roi Béhanzin, symbole de résistance.</t>
+          <t>La place Goho rend hommage à Béhanzin, dernier roi du Dahomey indépendant, figure de la résistance à la conquête coloniale. Sa statue monumentale accueille les visiteurs à l'entrée d'Abomey.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2285,7 +2280,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Grande forêt naturelle, observation d'animaux et de flore variée.</t>
+          <t>Au cœur de ses 16 000 hectares, la forêt de la Lama protège un noyau de forêt dense où vit le singe à ventre rouge, une espèce qu'on ne trouve qu'au Bénin. Une sortie nature à organiser avec un guide, entre Toffo et Zogbodomey.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2355,7 +2350,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Lieu de pèlerinage catholique niché dans les collines.</t>
+          <t>Nichée dans l'une des 41 collines de Dassa-Zoumé, la grotte Notre-Dame d'Arigbo est le plus grand lieu de pèlerinage du pays depuis 1954. Le week-end du 15 août, des milliers de fidèles y convergent ; le reste de l'année, le site invite au calme.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2435,7 +2430,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Ville traditionnelle marquée par la royauté locale et le culte vaudou.</t>
+          <t>Ancienne capitale du royaume mahi, Savalou mêle palais royal, fêtes de l'igname et cultes vaudou bien vivants. Le célèbre fétiche de Dankoli, à quelques kilomètres, attire des fidèles de toute la région.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2505,7 +2500,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Plage réputée du littoral béninois, tourisme balnéaire.</t>
+          <t>Entre le fleuve Mono et l'océan, Grand-Popo déroule ses kilomètres de sable bordés de cocotiers, à deux pas du Togo. L'endroit parfait pour décrocher un week-end, entre hôtels de plage et balades en lagune — attention aux courants, la baignade y est risquée.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2580,7 +2575,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Village au bord du lac Ahémé, source d'eau thermale.</t>
+          <t>Sur la rive du lac Ahémé, Possotomè est célèbre pour sa source thermale, dont l'eau minérale est embouteillée et vendue dans tout le pays. On y vient pour le calme, les balades en pirogue et les villages de pêcheurs alentour.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2660,7 +2655,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Embouchure spectaculaire entre océan, lagune et mangrove.</t>
+          <t>Là où le fleuve Mono rejoint l'Atlantique, la Bouche du Roy forme un delta d'îlots, de prairies et de mangroves parmi les mieux préservés du pays. Une excursion en pirogue d'une demi-journée, souvent conclue par des crevettes grillées.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2751,7 +2746,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Chef-lieu du département du Mono.</t>
+          <t>Chef-lieu du Mono, Lokossa est une ville carrefour vivante, point de départ pratique vers le lac Ahémé, Possotomè et la vallée du Mono.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2831,7 +2826,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Réserve faunique majeure, safaris et observation de la faune africaine.</t>
+          <t>Réserve de biosphère UNESCO depuis 1986, la Pendjari abrite la plus grande population d'éléphants d'Afrique de l'Ouest, ainsi que lions, guépards et hippopotames. Elle forme avec les parcs W et Arly le plus vaste écosystème intact de la région.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2892,6 +2887,11 @@
       <c r="U29" t="inlineStr">
         <is>
           <t>non</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Habitats traditionnels fortifiés des Batammariba.</t>
+          <t>Les tata somba, maisons-forteresses en terre à étage des Batammariba, ponctuent les collines entre Natitingou et Boukoumbé. Chaque tata reflète l'organisation familiale et spirituelle de ses habitants : une architecture unique, à découvrir avec un guide local.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Chutes d'eau et bassins naturels dans les montagnes de l'Atacora.</t>
+          <t>Au pied de la chaîne de l'Atacora, près de Tanguiéta, la chute de Tanougou plonge d'une quinzaine de mètres dans un bassin naturel propice à la baignade. Le débit varie fortement selon la saison : elle est à son plus beau après les pluies.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3032,6 +3032,11 @@
       <c r="U31" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Proche des zones frontalières formellement déconseillées du nord. Renseignez-vous sur la situation sécuritaire avant de partir.</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3061,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Musée sur les traditions socioculturelles de la région.</t>
+          <t>Dans un bâtiment colonial réhabilité, le musée régional présente l'habitat et les traditions de l'Atacora, avec des maquettes des différents types de tata somba. Le bon point de départ avant d'aller voir les vraies maisons dans les villages.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3136,7 +3141,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Massif montagneux, randonnée et paysages du nord-ouest du Bénin.</t>
+          <t>Le relief le plus marqué du Bénin, qui culmine vers 658 mètres au mont Sokbaro : falaises, vallées et villages perchés pour des randonnées de plusieurs heures. Un guide local est vivement conseillé.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -3187,6 +3192,11 @@
       <c r="U33" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Proche des zones frontalières formellement déconseillées du nord. Renseignez-vous sur la situation sécuritaire avant de partir.</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3221,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Réserve forestière et faunique de la région.</t>
+          <t>Plus de 100 000 hectares de forêts sèches, savanes et galeries forestières entre Bassila et Tchaourou, refuge de primates, d'antilopes et parfois du léopard. Une destination nature encore très sauvage, à explorer accompagné.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3286,7 +3296,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Commune forestière du sud de la Donga.</t>
+          <t>Commune forestière du sud de la Donga, Bassila sert de porte d'entrée vers la forêt de Wari-Maro et les paysages verdoyants du centre-ouest du pays.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3366,7 +3376,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Musée d'art et traditions populaires du nord du Bénin.</t>
+          <t>À ciel ouvert, ce musée ethnographique fait découvrir l'habitat traditionnel, les objets et les arts du nord du Bénin. Une visite courte et vivante au cœur de Parakou, la grande ville du Borgou.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3451,7 +3461,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Capitale historique des Batombu, siège royal.</t>
+          <t>Capitale historique des Baatonu (Bariba), Nikki accueille chaque année la Gaani, grande fête identitaire où cavaliers et dignitaires défilent devant le palais royal. Le reste du temps, la cour raconte l'histoire d'un royaume de cavaliers.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3521,7 +3531,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Parc transfrontalier Bénin-Niger-Burkina Faso, UNESCO.</t>
+          <t>Partagé entre le Bénin, le Niger et le Burkina Faso et classé à l'UNESCO, le parc W doit son nom aux méandres du fleuve Niger. Éléphants, buffles, hippopotames et oiseaux d'eau y peuplent savanes et zones humides.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3577,6 +3587,11 @@
       <c r="U38" t="inlineStr">
         <is>
           <t>non</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3616,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Rives du fleuve Niger, paysages et activités fluviales.</t>
+          <t>À Malanville, le fleuve Niger marque la frontière avec le Niger : rizières, pirogues et grand marché transfrontalier rythment la vie des rives. Un paysage sahélien, très différent du sud du pays.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3652,6 +3667,11 @@
       <c r="U39" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3696,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Chef-lieu du département de l'Alibori.</t>
+          <t>Chef-lieu de l'Alibori, Kandi est une ville du nord sahélien, carrefour d'élevage et de commerce sur la route du Niger.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3727,6 +3747,11 @@
       <c r="U40" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Proche des zones frontalières formellement déconseillées du nord. Renseignez-vous sur la situation sécuritaire avant de partir.</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3918,6 +3943,11 @@
           <t>Infos estimées</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Alerte</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3937,7 +3967,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hôtel bien noté proche de la plage, quartier des Ambassades.</t>
+          <t>Dans le quartier des Ambassades, à quelques pas de la mer, un hôtel bien noté pour séjourner à Cotonou au calme tout en restant proche du centre.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4019,7 +4049,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hôtel accessible, central à Cotonou.</t>
+          <t>Un hôtel central et sans chichis, pratique pour rayonner dans Cotonou à prix raisonnable.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4097,7 +4127,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hôtel avec accès direct à la plage.</t>
+          <t>Un hôtel avec accès direct à la plage, à Cotonou. Les avis en ligne sont très partagés selon les plateformes : regardez les commentaires récents avant de réserver.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4136,11 +4166,6 @@
       <c r="M4" t="n">
         <v>9</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Notes très divergentes selon la plateforme (2/5 TripAdvisor vs retours positifs ailleurs).</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Dès ≈ 30 USD / nuit (plateformes de réservation)</t>
@@ -4190,7 +4215,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Base nautique : kayak, jet-ski, activités familiales sur la Route des Pêches.</t>
+          <t>Une base nautique sur la Route des Pêches : kayak, jet-ski et activités en famille, à quelques minutes de Cotonou. De quoi passer une journée active entre lagune et océan.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4267,7 +4292,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Balade le long du littoral entre Cotonou et Ouidah.</t>
+          <t>Entre Cotonou et Ouidah, la Route des Pêches longe l'océan sur une quarantaine de kilomètres : villages de pêcheurs, cocoteraies, plages et maquis. À parcourir en voiture, à moto ou à vélo, en s'arrêtant au gré des envies.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4339,7 +4364,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Hôtel calme proche du centre historique de Ouidah.</t>
+          <t>Un hôtel calme à proximité du centre historique, pratique pour visiter Ouidah à pied.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4406,7 +4431,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hôtel haut de gamme dans des bâtiments coloniaux réhabilités.</t>
+          <t>Dans le quartier historique, un petit hôtel de charme de 14 chambres avec piscine, bibliothèque et bar, installé dans des bâtiments coloniaux réhabilités. L'adresse haut de gamme de Ouidah.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4488,7 +4513,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Hébergement paisible au bord du lac Ahémé, proche Ouidah.</t>
+          <t>Un hébergement paisible au bord du lac Ahémé, côté Kpomassè : nuits au calme, vue sur l'eau et balades en pirogue au départ de l'hôtel.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4514,11 +4539,6 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>+229 96 18 21 94</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Localisation précise : Kpomassè, lac Ahémé (à ~20 min de Ouidah)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -4565,7 +4585,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Parc d'attractions familial à Abomey-Calavi.</t>
+          <t>À Abomey-Calavi, un parc de détente et de loisirs pour souffler le temps d'un après-midi, en famille ou entre amis.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4637,7 +4657,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Circuit guidé sur l'histoire, le vaudou et la culture de Ouidah.</t>
+          <t>Une agence locale qui fait découvrir Ouidah autrement : histoire de la traite, temples et cérémonies vaudou, artisanat. Le guide adapte le circuit à votre temps et à vos centres d'intérêt.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4719,7 +4739,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Excursion en pirogue dans le village lacustre de Ganvié.</t>
+          <t>Au départ de l'embarcadère d'Abomey-Calavi, une pirogue à moteur ou à perche vous emmène à travers le lac Nokoué jusqu'à Ganvié. Comptez deux à quatre heures avec guide, tarif à négocier selon la taille du groupe.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4801,7 +4821,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Hôtel boutique moderne à Porto-Novo.</t>
+          <t>Un hôtel-boutique moderne à Porto-Novo, au décor soigné : l'adresse confortable pour découvrir la capitale.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4884,7 +4904,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Grand hôtel avec restaurant et piscine à Porto-Novo.</t>
+          <t>Grand hôtel de Porto-Novo avec piscine et restaurant, apprécié pour son rapport qualité-prix.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4967,7 +4987,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Parc récréatif familial à Porto-Novo.</t>
+          <t>À Porto-Novo, un parc récréatif où les enfants se dépensent pendant que les parents profitent de l'ombre.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -5034,7 +5054,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Excursion en pirogue sur la Rivière Noire, village d'artisans.</t>
+          <t>À Adjarra, à quelques kilomètres de Porto-Novo, une pirogue glisse sur la Rivière Noire sous les grands arbres, parmi poissons, reptiles et crocodiles nains. La sortie se termine souvent au marché des tam-tams, fabriqués par les artisans du village.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5101,7 +5121,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Immersion dans le grand marché local.</t>
+          <t>Reconstruit et inauguré en 2026, le grand marché de Ouando s'étend sur 3,5 hectares : tissus, épices, produits frais et artisanat. Plus animé le mercredi et le samedi matin.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5178,7 +5198,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Hôtel avec restaurant, l'un des mieux notés de Pobè.</t>
+          <t>L'un des hôtels les mieux notés de Pobè, avec restaurant : une halte pratique pour explorer le Plateau.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -5245,7 +5265,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Découverte de l'histoire de Kétou et des portes magiques.</t>
+          <t>Avec un guide, on découvre l'histoire de Kétou à travers la porte Akaba Idéna et ses légendes de protection magique. Le musée est en cours de réhabilitation : vérifiez l'accès avant de partir.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -5266,11 +5286,6 @@
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Vérifié (Google Places)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>En travaux de réhabilitation — accessibilité à vérifier.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -5317,7 +5332,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Immersion dans l'histoire yoruba-nago.</t>
+          <t>Une immersion dans la plus ancienne cité yoruba du pays : cour royale, remparts, autels et, avec un peu de chance, une sortie de masques guèlèdè.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -5384,7 +5399,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hôtel haut de gamme, l'un des mieux notés d'Abomey.</t>
+          <t>L'un des hôtels les mieux notés d'Abomey, idéal pour une nuit confortable après la visite des palais royaux.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -5451,7 +5466,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable proche du centre d'Abomey.</t>
+          <t>Un hôtel confortable proche du centre d'Abomey, bien placé pour enchaîner palais royaux et marché.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5529,7 +5544,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Maison d'hôtes chaleureuse à Abomey.</t>
+          <t>Une maison d'hôtes chaleureuse à Abomey, où l'on est reçu comme en famille : l'adresse idéale pour découvrir la ville au rythme local.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5612,7 +5627,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Guide local pour explorer l'histoire du royaume du Dahomey.</t>
+          <t>Un guide local fait revivre les douze rois du Dahomey, leurs palais, leurs bas-reliefs et les récits de la cour. Indispensable pour comprendre ce que l'on voit à Abomey.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5695,7 +5710,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Observation de la faune et de la flore.</t>
+          <t>Avec un guide, partez à la recherche du singe à ventre rouge, endémique du Bénin, dans le noyau de forêt dense de la Lama. Prévoyez de bonnes chaussures et un départ tôt le matin.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -5762,7 +5777,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable avec piscine à Dassa-Zoumé.</t>
+          <t>Un grand hôtel de plus de 100 chambres à Dassa-Zoumé, avec piscine, spa et restaurant : la halte confortable sur la route du nord.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5845,7 +5860,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Auberge bien située, halte pratique sur la route du nord.</t>
+          <t>Une auberge simple et bien située, l'étape pratique pour couper le long trajet entre le sud et le nord du pays.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5923,7 +5938,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable à Paouignan, près des collines.</t>
+          <t>Un hôtel confortable à Paouignan, au pied des collines, avec restaurant sur place.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6000,7 +6015,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Visite du site de pèlerinage catholique niché dans les collines.</t>
+          <t>Pèlerinage ou simple visite, la grotte d'Arigbo invite au recueillement au milieu des collines de Dassa. Le grand rassemblement a lieu le week-end du 15 août.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -6077,7 +6092,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Découverte d'un des sanctuaires vaudou les plus actifs d'Afrique de l'Ouest.</t>
+          <t>Près de Savalou, le fétiche de Dankoli est l'un des sanctuaires vaudou les plus fréquentés d'Afrique de l'Ouest : on y plante un bout de bois pour formuler un vœu, et l'on revient remercier s'il est exaucé. Une visite forte, à faire avec respect.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6144,7 +6159,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Immersion dans l'histoire du royaume Mahi.</t>
+          <t>Le palais royal de Savalou raconte l'histoire du royaume mahi et de ses souverains. Une visite courte, à combiner avec Dankoli et le centre de la ville.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -6211,7 +6226,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Hôtel-restaurant en bord de plage à Grand-Popo.</t>
+          <t>Hôtel-restaurant les pieds dans le sable à Grand-Popo, avec bungalows et vue sur l'océan : l'adresse détente du littoral ouest.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6299,7 +6314,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Hôtel proche de la plage, ambiance festive.</t>
+          <t>Proche de la plage de Grand-Popo, un hôtel à l'ambiance festive, apprécié des groupes d'amis.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -6366,7 +6381,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Grand complexe hôtelier en bord de mer.</t>
+          <t>Un grand complexe hôtelier en bord de mer à Grand-Popo, avec piscine et accès direct à la plage.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6444,7 +6459,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Agence locale pour circuits sur mesure dans la région.</t>
+          <t>Agence locale de Grand-Popo pour des circuits sur mesure : Bouche du Roy, villages de la lagune, lac Ahémé ou cultes vaudou.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6521,7 +6536,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Excursion vers l'embouchure entre océan et lagune.</t>
+          <t>Une remontée de la lagune d'environ deux heures jusqu'à l'embouchure du Mono, entre mangroves et îlots, avant une pause sur une île de pêcheurs.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6593,7 +6608,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Hôtel historique et chaleureux à Natitingou.</t>
+          <t>Un hôtel historique et chaleureux de Natitingou, connu aussi pour son restaurant.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -6671,7 +6686,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Hôtel au pied des collines, proche des villages Tata Somba.</t>
+          <t>Rénové et rouvert en 2024, l'hôtel Tata Somba est le grand hôtel public du nord, au pied des collines de l'Atacora, avec 25 chambres climatisées.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6744,7 +6759,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Hôtel avec piscine et vue sur les montagnes.</t>
+          <t>Un hôtel avec piscine et vue sur les montagnes de l'Atacora, pour se reposer entre deux excursions au départ de Natitingou.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6827,7 +6842,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Safari guidé pour observer lions, éléphants, hippopotames.</t>
+          <t>Safari guidé à l'aube ou en fin de journée, quand les animaux sont les plus actifs : éléphants, lions, hippopotames et antilopes de la savane soudanienne.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6888,6 +6903,11 @@
       <c r="T40" t="inlineStr">
         <is>
           <t>non</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6929,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Découverte des habitats fortifiés traditionnels.</t>
+          <t>Un guide de la région vous ouvre les portes des tata somba et explique la vie en famille dans ces maisons-forteresses à étage, entre greniers, autels et terrasses.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6976,7 +6996,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Baignade et randonnée dans un cadre naturel.</t>
+          <t>Une courte marche dans la végétation mène au bassin de la cascade, pour une baignade rafraîchissante au pied de l'Atacora.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -7022,6 +7042,11 @@
       <c r="T42" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Proche des zones frontalières formellement déconseillées du nord. Renseignez-vous sur la situation sécuritaire avant de partir.</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7068,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Hôtel familial réputé pour sa cuisine, à Djougou.</t>
+          <t>Un hôtel familial de Djougou, réputé pour sa cuisine.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -7115,7 +7140,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Hôtel simple et pratique à Djougou.</t>
+          <t>Un hôtel simple et pratique pour une nuit à Djougou.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -7193,7 +7218,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Hôtel accessible au centre de Djougou.</t>
+          <t>Un hôtel abordable au centre de Djougou, proche des commerces.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7265,7 +7290,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Randonnée nature et observation de la faune.</t>
+          <t>Randonnée accompagnée dans l'une des plus vastes forêts classées du pays, à l'affût des primates, des antilopes et des oiseaux.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -7332,7 +7357,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Hôtel confortable et bien noté à Parakou.</t>
+          <t>Un hôtel confortable et bien noté à Parakou, pour une étape soignée dans le nord.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -7399,7 +7424,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Grand hôtel avec piscine à Parakou.</t>
+          <t>Grand hôtel avec piscine à Parakou, pratique pour les séjours en famille comme pour les déplacements professionnels.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7472,7 +7497,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Hôtel au décor traditionnel, très bien noté à Parakou.</t>
+          <t>Un hôtel au décor traditionnel, parmi les mieux notés de Parakou, qui offre une vraie touche locale.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7545,7 +7570,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Découverte de l'art et des traditions du nord du Bénin.</t>
+          <t>Visite guidée des habitats et objets traditionnels du nord du Bénin, à ciel ouvert, au cœur de Parakou.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7627,7 +7652,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Hôtel propre et sécurisé à Malanville.</t>
+          <t>Un hôtel propre et sécurisé à Malanville, près de la frontière avec le Niger.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7673,6 +7698,11 @@
       <c r="T51" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7724,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Observation de la faune dans le parc transfrontalier UNESCO.</t>
+          <t>Observation de la faune du parc W, entre savanes et méandres du fleuve Niger : éléphants, buffles, hippopotames et oiseaux d'eau.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7750,6 +7780,11 @@
       <c r="T52" t="inlineStr">
         <is>
           <t>non</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
     </row>

--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,21 @@
           <t>Alerte</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Photo crédit</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Photo source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -866,6 +881,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Jeunes_sur_la_plage_de_Fidjross%C3%A8_%C3%A0_Cotonou_au_B%C3%A9nin.jpg/1920px-Jeunes_sur_la_plage_de_Fidjross%C3%A8_%C3%A0_Cotonou_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Photo : Saliousoft — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Jeunes_sur_la_plage_de_Fidjross%C3%A8_%C3%A0_Cotonou_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -947,6 +977,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Vue_de_gauche_de_la_statue_%C3%A0_la_Place_du_souvenir.jpg/1920px-Vue_de_gauche_de_la_statue_%C3%A0_la_Place_du_souvenir.jpg</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Photo : Rachad sanoussi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Vue_de_gauche_de_la_statue_%C3%A0_la_Place_du_souvenir.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1114,6 +1159,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Route_des_esclaves_%C3%A0_Ouidah_au_B%C3%A9nin.jpg/1920px-Route_des_esclaves_%C3%A0_Ouidah_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Photo : Hinnou Gontran Serge — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Route_des_esclaves_%C3%A0_Ouidah_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1205,6 +1265,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Temple_des_Pythons_de_Ouidah_02.jpg/1920px-Temple_des_Pythons_de_Ouidah_02.jpg</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Photo : Gildaskiki — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Temple_des_Pythons_de_Ouidah_02.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1286,6 +1361,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/f/f8/Foret_Sacree_de_Kpasse_%2820733814183%29.jpg</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Photo : David Stanley from Nanaimo, Canada — CC BY 2.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Foret_Sacree_de_Kpasse_(20733814183).jpg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1372,6 +1462,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Le_Fort_Portugais_de_Ouidah.jpg/1920px-Le_Fort_Portugais_de_Ouidah.jpg</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Photo : Rachad sanoussi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Le_Fort_Portugais_de_Ouidah.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1453,6 +1558,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Pilotis_of_Ganvi%C3%A9_People.jpg/1920px-Pilotis_of_Ganvi%C3%A9_People.jpg</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Photo : jbdodane — CC BY 2.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Pilotis_of_Ganvi%C3%A9_People.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1534,6 +1654,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a0/Une_vue_de_proche_de_la_devanture_du_Mus%C3%A9e_Honm%C3%A8.jpg/1920px-Une_vue_de_proche_de_la_devanture_du_Mus%C3%A9e_Honm%C3%A8.jpg</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Photo : Rachad sanoussi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Une_vue_de_proche_de_la_devanture_du_Mus%C3%A9e_Honm%C3%A8.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1615,6 +1750,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/Mus%C3%A9e_da_Silva.jpg/1920px-Mus%C3%A9e_da_Silva.jpg</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Photo : Ksperentos — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Mus%C3%A9e_da_Silva.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1866,6 +2016,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/Cath%C3%A9drale_Notre-Dame_de_l%27Immacul%C3%A9e_Conception_de_Porto-Novo_2021_01.jpg/1920px-Cath%C3%A9drale_Notre-Dame_de_l%27Immacul%C3%A9e_Conception_de_Porto-Novo_2021_01.jpg</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Photo : Mhope2010 — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Cath%C3%A9drale_Notre-Dame_de_l%27Immacul%C3%A9e_Conception_de_Porto-Novo_2021_01.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2006,6 +2171,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg/1920px-La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Photo : Rachad sanoussi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2172,6 +2352,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Palais_royaux_d%27Abomey_3.jpg/1920px-Palais_royaux_d%27Abomey_3.jpg</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Photo : Azogbonon — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Palais_royaux_d%27Abomey_3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2328,6 +2523,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/All%C3%A9e_verte_pour_des_circuits_%C3%A9cotouristiques_dans_la_for%C3%AAts_de_la_Lama_dans_la_commune_de_Zogbodomey_au_B%C3%A9nin.jpg/1920px-All%C3%A9e_verte_pour_des_circuits_%C3%A9cotouristiques_dans_la_for%C3%AAts_de_la_Lama_dans_la_commune_de_Zogbodomey_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Photo : Padonou Dotou — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:All%C3%A9e_verte_pour_des_circuits_%C3%A9cotouristiques_dans_la_for%C3%AAts_de_la_Lama_dans_la_commune_de_Zogbodomey_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2553,6 +2763,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Plage_de_Grand-Popo_en_fin_de_journ%C3%A9e_%281%29.jpg/1920px-Plage_de_Grand-Popo_en_fin_de_journ%C3%A9e_%281%29.jpg</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Photo : Ji-Elle — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Plage_de_Grand-Popo_en_fin_de_journ%C3%A9e_(1).jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2894,6 +3119,21 @@
           <t>Zone formellement déconseillée aux voyageurs (risque d'attaques terroristes et d'enlèvements, frontière nord). Vérifiez les conseils aux voyageurs de votre pays avant tout déplacement.</t>
         </is>
       </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/14/Une_vue_du_Parc_de_la_Pendjari.jpg/1920px-Une_vue_du_Parc_de_la_Pendjari.jpg</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Photo : Gildasjr — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Une_vue_du_Parc_de_la_Pendjari.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3039,6 +3279,21 @@
           <t>Proche des zones frontalières formellement déconseillées du nord. Renseignez-vous sur la situation sécuritaire avant de partir.</t>
         </is>
       </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Chutes_de_Tanongou.jpg/1920px-Chutes_de_Tanongou.jpg</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Photo : KOUAGOU Damien — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Chutes_de_Tanongou.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3117,6 +3372,21 @@
       <c r="U32" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/MUS%C3%89E_R%C3%89GIONAL_DE_NATITINGOU.jpg/1920px-MUS%C3%89E_R%C3%89GIONAL_DE_NATITINGOU.jpg</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Photo : Farid AMADOU BAHLEMAN — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:MUS%C3%89E_R%C3%89GIONAL_DE_NATITINGOU.jpg</t>
         </is>
       </c>
     </row>
@@ -3829,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:X56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3948,6 +4218,21 @@
           <t>Alerte</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Photo crédit</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Photo source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4802,6 +5087,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Pilotis_of_Ganvi%C3%A9_People.jpg/1920px-Pilotis_of_Ganvi%C3%A9_People.jpg</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Photo : jbdodane — CC BY 2.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Pilotis_of_Ganvi%C3%A9_People.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5102,6 +5402,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b8/La_rivi%C3%A8re_noire_au_sud_du_B%C3%A9nin_06.jpg/1920px-La_rivi%C3%A8re_noire_au_sud_du_B%C3%A9nin_06.jpg</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Photo : Fawaz.tairou — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:La_rivi%C3%A8re_noire_au_sud_du_B%C3%A9nin_06.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5313,6 +5628,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg/1920px-La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Photo : Rachad sanoussi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5380,6 +5710,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg/1920px-La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Photo : Rachad sanoussi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:La_porte_pour_femme_du_mus%C3%A9e_Akaba_idena.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5691,6 +6036,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/H%C3%A9ritage_des_rois_du_Danxom%C3%A9_%C3%A0_travers_leurs_palais_02.jpg/1920px-H%C3%A9ritage_des_rois_du_Danxom%C3%A9_%C3%A0_travers_leurs_palais_02.jpg</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Photo : Zokoluc11 — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:H%C3%A9ritage_des_rois_du_Danxom%C3%A9_%C3%A0_travers_leurs_palais_02.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5758,6 +6118,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/All%C3%A9e_verte_pour_des_circuits_%C3%A9cotouristiques_dans_la_for%C3%AAts_de_la_Lama_dans_la_commune_de_Zogbodomey_au_B%C3%A9nin.jpg/1920px-All%C3%A9e_verte_pour_des_circuits_%C3%A9cotouristiques_dans_la_for%C3%AAts_de_la_Lama_dans_la_commune_de_Zogbodomey_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Photo : Padonou Dotou — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:All%C3%A9e_verte_pour_des_circuits_%C3%A9cotouristiques_dans_la_for%C3%AAts_de_la_Lama_dans_la_commune_de_Zogbodomey_au_B%C3%A9nin.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6295,6 +6670,21 @@
           <t>non</t>
         </is>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Grand-Popo-Awal%C3%A9_Plage.jpg/1920px-Grand-Popo-Awal%C3%A9_Plage.jpg</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Photo : Ji-Elle — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Grand-Popo-Awal%C3%A9_Plage.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6823,6 +7213,21 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Vue_de_la_piscine_de_l%27h%C3%B4tel_Totora_de_Natitingou.jpg/1920px-Vue_de_la_piscine_de_l%27h%C3%B4tel_Totora_de_Natitingou.jpg</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Photo : Barke11 — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Vue_de_la_piscine_de_l%27h%C3%B4tel_Totora_de_Natitingou.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7049,6 +7454,21 @@
           <t>Proche des zones frontalières formellement déconseillées du nord. Renseignez-vous sur la situation sécuritaire avant de partir.</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Chutes_de_Tanongou.jpg/1920px-Chutes_de_Tanongou.jpg</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Photo : KOUAGOU Damien — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Chutes_de_Tanongou.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -7476,6 +7896,21 @@
       <c r="T48" t="inlineStr">
         <is>
           <t>oui</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Kobourou_city_H%C3%B4tel_Parakou.jpg/1920px-Kobourou_city_H%C3%B4tel_Parakou.jpg</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Photo : Africasounvi — CC BY-SA 4.0, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Kobourou_city_H%C3%B4tel_Parakou.jpg</t>
         </is>
       </c>
     </row>

--- a/benin_contenu_curation.xlsx
+++ b/benin_contenu_curation.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Z43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -629,6 +629,11 @@
           <t>Photo source</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Restauration sur place</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1932,6 +1937,11 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
@@ -4099,7 +4109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:Y56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4233,6 +4243,11 @@
           <t>Photo source</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Restauration sur place</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5268,6 +5283,11 @@
           <t>non</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -5561,6 +5581,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -6216,6 +6241,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6371,6 +6401,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6685,6 +6720,11 @@
           <t>https://commons.wikimedia.org/wiki/File:Grand-Popo-Awal%C3%A9_Plage.jpg</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -7057,6 +7097,11 @@
           <t>oui</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7537,6 +7582,11 @@
         </is>
       </c>
       <c r="T43" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
